--- a/PROPERTIES/QYOTA/QYOTA 2025.xlsx
+++ b/PROPERTIES/QYOTA/QYOTA 2025.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="423">
   <si>
     <t xml:space="preserve">COURTLAND REALTORS LTD P.O.BOX 11993, NAIROBI</t>
   </si>
@@ -1282,6 +1282,12 @@
     <t xml:space="preserve">‘0700481989</t>
   </si>
   <si>
+    <t xml:space="preserve">14/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGE3X44IB3</t>
+  </si>
+  <si>
     <t xml:space="preserve">SYLVIA MURULE</t>
   </si>
   <si>
@@ -1289,6 +1295,9 @@
   </si>
   <si>
     <t xml:space="preserve">TG269FNRFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGT COMM 5% </t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1313,7 @@
     <numFmt numFmtId="169" formatCode="#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1492,6 +1501,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1572,7 +1588,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="119">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2041,6 +2057,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4908,20 +4932,26 @@
       </c>
       <c r="H36" s="61"/>
       <c r="I36" s="61"/>
-      <c r="J36" s="114"/>
+      <c r="J36" s="114" t="n">
+        <v>12250</v>
+      </c>
       <c r="K36" s="61"/>
       <c r="L36" s="10"/>
       <c r="M36" s="10"/>
       <c r="N36" s="10"/>
-      <c r="O36" s="85"/>
-      <c r="P36" s="97"/>
+      <c r="O36" s="85" t="s">
+        <v>417</v>
+      </c>
+      <c r="P36" s="97" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="68" t="n">
         <v>31</v>
       </c>
       <c r="B37" s="87" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C37" s="115" t="s">
         <v>415</v>
@@ -4949,7 +4979,7 @@
         <v>45876</v>
       </c>
       <c r="P37" s="97" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4957,7 +4987,7 @@
         <v>32</v>
       </c>
       <c r="B38" s="99" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C38" s="100" t="n">
         <v>707653219</v>
@@ -4983,7 +5013,7 @@
         <v>45695</v>
       </c>
       <c r="P38" s="97" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5012,7 +5042,10 @@
       <c r="B40" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="76"/>
+      <c r="C40" s="117" t="n">
+        <f aca="false">SUM(J8:J38)</f>
+        <v>207300</v>
+      </c>
       <c r="E40" s="77"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5036,7 +5069,7 @@
       <c r="B43" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="80"/>
+      <c r="C43" s="118"/>
       <c r="F43" s="78"/>
       <c r="G43" s="78"/>
       <c r="H43" s="78"/>
@@ -5047,7 +5080,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="18" t="s">
-        <v>88</v>
+        <v>422</v>
       </c>
       <c r="C45" s="68"/>
     </row>

--- a/PROPERTIES/QYOTA/QYOTA 2025.xlsx
+++ b/PROPERTIES/QYOTA/QYOTA 2025.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="428">
   <si>
     <t xml:space="preserve">COURTLAND REALTORS LTD P.O.BOX 11993, NAIROBI</t>
   </si>
@@ -1228,6 +1228,12 @@
     <t xml:space="preserve">TG37F6EEQH</t>
   </si>
   <si>
+    <t xml:space="preserve">21/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFJ6IUAC8I</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRISCILLA NDIRANGU</t>
   </si>
   <si>
@@ -1280,6 +1286,15 @@
   </si>
   <si>
     <t xml:space="preserve">‘0700481989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGK9TW8MVR</t>
   </si>
   <si>
     <t xml:space="preserve">14/07/2025</t>
@@ -1313,7 +1328,7 @@
     <numFmt numFmtId="169" formatCode="#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1465,8 +1480,37 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
-      <sz val="12"/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
       <color rgb="FF00A933"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1474,7 +1518,14 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="12"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1482,20 +1533,40 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="12"/>
-      <name val="Calibri Light"/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="14"/>
       <name val="Calibri Light"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
+      <sz val="14"/>
+      <name val="Calibri Light"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri Light"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1503,10 +1574,12 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="12"/>
+      <i val="true"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1588,7 +1661,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="163">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1937,107 +2010,155 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2045,23 +2166,151 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="26" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="24" fillId="2" borderId="4" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3844,14 +4093,20 @@
   <dimension ref="A1:P48"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="29.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="21.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="26.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="21.56"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="87" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="88" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="88" width="27.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="88" width="20.97"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="5" style="87" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="88" width="19.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="88" width="17.23"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="10" style="87" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="88" width="21.32"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="13" style="87" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="88" width="26.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="15" style="87" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="88" width="21.56"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="87" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3875,7 +4130,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="3"/>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="88" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3889,13 +4144,13 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="3"/>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="88" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="89"/>
       <c r="C4" s="6" t="s">
         <v>5</v>
       </c>
@@ -3905,1202 +4160,1214 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="9" t="s">
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+    </row>
+    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="90"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="I5" s="92"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="93"/>
+      <c r="M5" s="93"/>
+      <c r="N5" s="93"/>
+      <c r="O5" s="93"/>
+      <c r="P5" s="93"/>
+    </row>
+    <row r="6" customFormat="false" ht="29.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="92" t="s">
         <v>395</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="91" t="s">
         <v>396</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="90" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="n">
+    <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="87" t="s">
+      <c r="B7" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="88" t="n">
+      <c r="C7" s="97" t="n">
         <v>703485579</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="98" t="n">
         <v>10000</v>
       </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="70"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="84"/>
-      <c r="P7" s="18"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="n">
+      <c r="E7" s="99"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="101"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="89"/>
+      <c r="M7" s="89"/>
+      <c r="N7" s="89"/>
+      <c r="O7" s="102"/>
+      <c r="P7" s="103"/>
+    </row>
+    <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="104" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="89" t="s">
+      <c r="B8" s="105" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="90" t="n">
+      <c r="C8" s="106" t="n">
         <v>726646115</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="107" t="n">
         <v>10000</v>
       </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="23" t="n">
+      <c r="E8" s="108"/>
+      <c r="F8" s="109" t="n">
         <v>10750</v>
       </c>
-      <c r="G8" s="22" t="n">
-        <v>250</v>
-      </c>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="84"/>
-      <c r="P8" s="50"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="27" t="n">
+      <c r="G8" s="108" t="n">
+        <v>250</v>
+      </c>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="89"/>
+      <c r="K8" s="108"/>
+      <c r="L8" s="110"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="110"/>
+      <c r="O8" s="102"/>
+      <c r="P8" s="111"/>
+    </row>
+    <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="112" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="92" t="n">
+      <c r="C9" s="114" t="n">
         <v>725840501</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" s="115" t="n">
         <v>10000</v>
       </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="31" t="n">
-        <v>250</v>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>250</v>
-      </c>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="93" t="n">
+      <c r="E9" s="116"/>
+      <c r="F9" s="117" t="n">
+        <v>250</v>
+      </c>
+      <c r="G9" s="108" t="n">
+        <v>250</v>
+      </c>
+      <c r="H9" s="115"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="118" t="n">
         <v>10250</v>
       </c>
-      <c r="K9" s="30"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="84" t="n">
+      <c r="K9" s="116"/>
+      <c r="L9" s="110"/>
+      <c r="M9" s="110"/>
+      <c r="N9" s="110"/>
+      <c r="O9" s="102" t="n">
         <v>45723</v>
       </c>
-      <c r="P9" s="94" t="s">
+      <c r="P9" s="119" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="n">
+    <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="104" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="95" t="s">
+      <c r="B10" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="96" t="n">
+      <c r="C10" s="120" t="n">
         <v>706082031</v>
       </c>
-      <c r="D10" s="24" t="n">
+      <c r="D10" s="107" t="n">
         <v>10000</v>
       </c>
-      <c r="E10" s="22"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="22" t="n">
-        <v>250</v>
-      </c>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="93" t="n">
+      <c r="E10" s="108"/>
+      <c r="F10" s="109"/>
+      <c r="G10" s="108" t="n">
+        <v>250</v>
+      </c>
+      <c r="H10" s="107"/>
+      <c r="I10" s="107"/>
+      <c r="J10" s="118" t="n">
         <v>10750</v>
       </c>
-      <c r="K10" s="22"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="84" t="n">
+      <c r="K10" s="108"/>
+      <c r="L10" s="110"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="102" t="n">
         <v>45723</v>
       </c>
-      <c r="P10" s="97" t="s">
+      <c r="P10" s="121" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="n">
+    <row r="11" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="104" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="95" t="s">
+      <c r="B11" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="96"/>
-      <c r="D11" s="24" t="n">
+      <c r="C11" s="120"/>
+      <c r="D11" s="107" t="n">
         <v>10000</v>
       </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="22" t="n">
-        <v>250</v>
-      </c>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="93"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="85"/>
-      <c r="P11" s="97"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="n">
+      <c r="E11" s="108"/>
+      <c r="F11" s="109"/>
+      <c r="G11" s="108" t="n">
+        <v>250</v>
+      </c>
+      <c r="H11" s="107"/>
+      <c r="I11" s="107"/>
+      <c r="J11" s="118"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="110"/>
+      <c r="M11" s="110"/>
+      <c r="N11" s="110"/>
+      <c r="O11" s="122"/>
+      <c r="P11" s="121"/>
+    </row>
+    <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="104" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="89" t="s">
+      <c r="B12" s="105" t="s">
         <v>212</v>
       </c>
-      <c r="C12" s="90" t="n">
+      <c r="C12" s="106" t="n">
         <v>796721103</v>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D12" s="123" t="n">
         <v>9500</v>
       </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="22" t="n">
-        <v>250</v>
-      </c>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="84"/>
-      <c r="P12" s="97"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="n">
+      <c r="E12" s="104"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="108" t="n">
+        <v>250</v>
+      </c>
+      <c r="H12" s="104"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="118"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="110"/>
+      <c r="M12" s="110"/>
+      <c r="N12" s="110"/>
+      <c r="O12" s="102"/>
+      <c r="P12" s="121"/>
+    </row>
+    <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="104" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="95" t="s">
+      <c r="B13" s="105" t="s">
         <v>136</v>
       </c>
-      <c r="C13" s="96" t="n">
+      <c r="C13" s="120" t="n">
         <v>792896940</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="107" t="n">
         <v>9500</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="22" t="n">
-        <v>250</v>
-      </c>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="93"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="84"/>
-      <c r="P13" s="94"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="n">
+      <c r="E13" s="108"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="108" t="n">
+        <v>250</v>
+      </c>
+      <c r="H13" s="107"/>
+      <c r="I13" s="107"/>
+      <c r="J13" s="118" t="n">
+        <v>9500</v>
+      </c>
+      <c r="K13" s="108"/>
+      <c r="L13" s="110"/>
+      <c r="M13" s="110"/>
+      <c r="N13" s="110"/>
+      <c r="O13" s="102" t="s">
+        <v>399</v>
+      </c>
+      <c r="P13" s="119" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="104" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="98" t="s">
+      <c r="B14" s="124" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="96" t="n">
+      <c r="C14" s="120" t="n">
         <v>728513304</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="107" t="n">
         <v>10000</v>
       </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="23" t="n">
+      <c r="E14" s="108"/>
+      <c r="F14" s="109" t="n">
         <v>10500</v>
       </c>
-      <c r="G14" s="22" t="n">
-        <v>250</v>
-      </c>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="93"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="84"/>
-      <c r="P14" s="94"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="n">
+      <c r="G14" s="108" t="n">
+        <v>250</v>
+      </c>
+      <c r="H14" s="107"/>
+      <c r="I14" s="107"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="108"/>
+      <c r="L14" s="110"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="110"/>
+      <c r="O14" s="102"/>
+      <c r="P14" s="119"/>
+    </row>
+    <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="89" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="99" t="s">
-        <v>399</v>
-      </c>
-      <c r="C15" s="100" t="n">
+      <c r="B15" s="96" t="s">
+        <v>401</v>
+      </c>
+      <c r="C15" s="125" t="n">
         <v>710621587</v>
       </c>
-      <c r="D15" s="16" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E15" s="14"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="93" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="84" t="n">
+      <c r="D15" s="98" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E15" s="99"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H15" s="98"/>
+      <c r="I15" s="98"/>
+      <c r="J15" s="118" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K15" s="99"/>
+      <c r="L15" s="93"/>
+      <c r="M15" s="93"/>
+      <c r="N15" s="93"/>
+      <c r="O15" s="102" t="n">
         <v>45845</v>
       </c>
-      <c r="P15" s="101" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="n">
+      <c r="P15" s="126" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="89" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="99" t="s">
+      <c r="B16" s="96" t="s">
         <v>298</v>
       </c>
-      <c r="C16" s="100" t="n">
+      <c r="C16" s="125" t="n">
         <v>768218105</v>
       </c>
-      <c r="D16" s="16" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E16" s="14"/>
-      <c r="F16" s="15" t="n">
+      <c r="D16" s="98" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E16" s="99"/>
+      <c r="F16" s="100" t="n">
         <v>9500</v>
       </c>
-      <c r="G16" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="93" t="n">
+      <c r="G16" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H16" s="98"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="118" t="n">
         <v>10500</v>
       </c>
-      <c r="K16" s="14"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="84" t="n">
+      <c r="K16" s="99"/>
+      <c r="L16" s="127"/>
+      <c r="M16" s="93"/>
+      <c r="N16" s="93"/>
+      <c r="O16" s="102" t="n">
         <v>-648086</v>
       </c>
-      <c r="P16" s="97" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="n">
+      <c r="P16" s="121" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="104" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="95" t="s">
+      <c r="B17" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="96" t="n">
+      <c r="C17" s="120" t="n">
         <v>703706971</v>
       </c>
-      <c r="D17" s="24" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="93" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K17" s="22"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="84" t="n">
+      <c r="D17" s="107" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E17" s="108"/>
+      <c r="F17" s="109"/>
+      <c r="G17" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H17" s="107"/>
+      <c r="I17" s="107"/>
+      <c r="J17" s="118" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K17" s="108"/>
+      <c r="L17" s="110"/>
+      <c r="M17" s="110"/>
+      <c r="N17" s="110"/>
+      <c r="O17" s="102" t="n">
         <v>45784</v>
       </c>
-      <c r="P17" s="94" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="n">
+      <c r="P17" s="119" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="104" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="95" t="s">
+      <c r="B18" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="96" t="n">
+      <c r="C18" s="120" t="n">
         <v>727026360</v>
       </c>
-      <c r="D18" s="24" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="93" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K18" s="22"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="84" t="n">
+      <c r="D18" s="107" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E18" s="108"/>
+      <c r="F18" s="109"/>
+      <c r="G18" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H18" s="107"/>
+      <c r="I18" s="107"/>
+      <c r="J18" s="118" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K18" s="108"/>
+      <c r="L18" s="110"/>
+      <c r="M18" s="110"/>
+      <c r="N18" s="110"/>
+      <c r="O18" s="102" t="n">
         <v>45876</v>
       </c>
-      <c r="P18" s="94" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="n">
+      <c r="P18" s="119" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="104" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="95" t="s">
+      <c r="B19" s="105" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="102" t="n">
+      <c r="C19" s="106" t="n">
         <v>739314188</v>
       </c>
-      <c r="D19" s="24" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="23" t="n">
+      <c r="D19" s="107" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E19" s="108"/>
+      <c r="F19" s="109" t="n">
         <v>41500</v>
       </c>
-      <c r="G19" s="22" t="n">
-        <v>250</v>
-      </c>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="93"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="85"/>
-      <c r="P19" s="103"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="n">
+      <c r="G19" s="108" t="n">
+        <v>250</v>
+      </c>
+      <c r="H19" s="107"/>
+      <c r="I19" s="107"/>
+      <c r="J19" s="118"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="128"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="122"/>
+      <c r="P19" s="129"/>
+    </row>
+    <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="104" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="95" t="s">
+      <c r="B20" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="102" t="n">
+      <c r="C20" s="106" t="n">
         <v>111236304</v>
       </c>
-      <c r="D20" s="34" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="22" t="n">
-        <v>250</v>
-      </c>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="93" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K20" s="19"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="25"/>
-      <c r="O20" s="84" t="n">
+      <c r="D20" s="123" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E20" s="104"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="108" t="n">
+        <v>250</v>
+      </c>
+      <c r="H20" s="130"/>
+      <c r="I20" s="130"/>
+      <c r="J20" s="118" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K20" s="104"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="102" t="n">
         <v>45784</v>
       </c>
-      <c r="P20" s="82" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27" t="n">
+      <c r="P20" s="131" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="112" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="91" t="s">
+      <c r="B21" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="102" t="n">
+      <c r="C21" s="106" t="n">
         <v>723022756</v>
       </c>
-      <c r="D21" s="32" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="31" t="n">
+      <c r="D21" s="115" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E21" s="116"/>
+      <c r="F21" s="117" t="n">
         <v>20150</v>
       </c>
-      <c r="G21" s="22" t="n">
-        <v>250</v>
-      </c>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="93" t="n">
+      <c r="G21" s="108" t="n">
+        <v>250</v>
+      </c>
+      <c r="H21" s="115"/>
+      <c r="I21" s="115"/>
+      <c r="J21" s="118" t="n">
         <v>17300</v>
       </c>
-      <c r="K21" s="30"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="84" t="n">
+      <c r="K21" s="116"/>
+      <c r="L21" s="110"/>
+      <c r="M21" s="110"/>
+      <c r="N21" s="110"/>
+      <c r="O21" s="102" t="n">
         <v>45695</v>
       </c>
-      <c r="P21" s="103" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="n">
+      <c r="P21" s="129" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="104" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="95" t="s">
+      <c r="B22" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="96" t="n">
+      <c r="C22" s="120" t="n">
         <v>705321457</v>
       </c>
-      <c r="D22" s="24" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="23" t="n">
-        <v>11250</v>
-      </c>
-      <c r="G22" s="22" t="n">
-        <v>250</v>
-      </c>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="93"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="84"/>
-      <c r="P22" s="97"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="n">
+      <c r="D22" s="107" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E22" s="108"/>
+      <c r="F22" s="109" t="n">
+        <v>11250</v>
+      </c>
+      <c r="G22" s="108" t="n">
+        <v>250</v>
+      </c>
+      <c r="H22" s="107"/>
+      <c r="I22" s="107"/>
+      <c r="J22" s="118"/>
+      <c r="K22" s="108"/>
+      <c r="L22" s="110"/>
+      <c r="M22" s="110"/>
+      <c r="N22" s="110"/>
+      <c r="O22" s="102"/>
+      <c r="P22" s="121"/>
+    </row>
+    <row r="23" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="89" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="99" t="s">
+      <c r="B23" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="100" t="n">
+      <c r="C23" s="125" t="n">
         <v>726518863</v>
       </c>
-      <c r="D23" s="16" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="93" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K23" s="14"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="84" t="n">
+      <c r="D23" s="98" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E23" s="99"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H23" s="98"/>
+      <c r="I23" s="98"/>
+      <c r="J23" s="118" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K23" s="99"/>
+      <c r="L23" s="93"/>
+      <c r="M23" s="93"/>
+      <c r="N23" s="93"/>
+      <c r="O23" s="102" t="n">
         <v>45845</v>
       </c>
-      <c r="P23" s="104" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="n">
+      <c r="P23" s="132" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="89" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="99" t="s">
+      <c r="B24" s="96" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="100" t="n">
+      <c r="C24" s="125" t="n">
         <v>727516082</v>
       </c>
-      <c r="D24" s="16" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="93" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K24" s="14"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="84" t="n">
+      <c r="D24" s="98" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E24" s="99"/>
+      <c r="F24" s="100"/>
+      <c r="G24" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H24" s="98"/>
+      <c r="I24" s="98"/>
+      <c r="J24" s="118" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K24" s="99"/>
+      <c r="L24" s="127"/>
+      <c r="M24" s="93"/>
+      <c r="N24" s="93"/>
+      <c r="O24" s="102" t="n">
         <v>45754</v>
       </c>
-      <c r="P24" s="97" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="n">
+      <c r="P24" s="121" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="104" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="95" t="s">
+      <c r="B25" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="96" t="n">
+      <c r="C25" s="120" t="n">
         <v>706651018</v>
       </c>
-      <c r="D25" s="24" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E25" s="22"/>
-      <c r="F25" s="23" t="n">
+      <c r="D25" s="107" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E25" s="108"/>
+      <c r="F25" s="109" t="n">
         <v>12050</v>
       </c>
-      <c r="G25" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="93"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="86"/>
-      <c r="P25" s="94"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="n">
+      <c r="G25" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H25" s="107"/>
+      <c r="I25" s="107"/>
+      <c r="J25" s="118"/>
+      <c r="K25" s="108"/>
+      <c r="L25" s="110"/>
+      <c r="M25" s="110"/>
+      <c r="N25" s="110"/>
+      <c r="O25" s="133"/>
+      <c r="P25" s="119"/>
+    </row>
+    <row r="26" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="89" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="99" t="s">
+      <c r="B26" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="100" t="n">
+      <c r="C26" s="125" t="n">
         <v>718723801</v>
       </c>
-      <c r="D26" s="16" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="93" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K26" s="14"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="84" t="n">
+      <c r="D26" s="98" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E26" s="99"/>
+      <c r="F26" s="100"/>
+      <c r="G26" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H26" s="98"/>
+      <c r="I26" s="98"/>
+      <c r="J26" s="118" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K26" s="99"/>
+      <c r="L26" s="89"/>
+      <c r="M26" s="89"/>
+      <c r="N26" s="89"/>
+      <c r="O26" s="102" t="n">
         <v>45723</v>
       </c>
-      <c r="P26" s="105" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="n">
+      <c r="P26" s="134" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="104" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="95" t="s">
+      <c r="B27" s="105" t="s">
         <v>154</v>
       </c>
-      <c r="C27" s="102" t="n">
+      <c r="C27" s="106" t="n">
         <v>729400661</v>
       </c>
-      <c r="D27" s="24" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E27" s="22"/>
-      <c r="F27" s="23" t="n">
+      <c r="D27" s="107" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E27" s="108"/>
+      <c r="F27" s="109" t="n">
         <v>1750</v>
       </c>
-      <c r="G27" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H27" s="52"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="93" t="n">
+      <c r="G27" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H27" s="135"/>
+      <c r="I27" s="107"/>
+      <c r="J27" s="118" t="n">
         <v>10500</v>
       </c>
-      <c r="K27" s="22"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="25"/>
-      <c r="N27" s="25"/>
-      <c r="O27" s="84" t="n">
+      <c r="K27" s="108"/>
+      <c r="L27" s="110"/>
+      <c r="M27" s="110"/>
+      <c r="N27" s="110"/>
+      <c r="O27" s="102" t="n">
         <v>45695</v>
       </c>
-      <c r="P27" s="97" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="n">
+      <c r="P27" s="121" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="104" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="95" t="s">
-        <v>410</v>
-      </c>
-      <c r="C28" s="102" t="n">
+      <c r="B28" s="105" t="s">
+        <v>412</v>
+      </c>
+      <c r="C28" s="106" t="n">
         <v>101921686</v>
       </c>
-      <c r="D28" s="24" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E28" s="22"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="93" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K28" s="22"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25"/>
-      <c r="N28" s="25"/>
-      <c r="O28" s="67" t="n">
+      <c r="D28" s="107" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E28" s="108"/>
+      <c r="F28" s="109"/>
+      <c r="G28" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H28" s="107"/>
+      <c r="I28" s="107"/>
+      <c r="J28" s="118" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K28" s="108"/>
+      <c r="L28" s="110"/>
+      <c r="M28" s="110"/>
+      <c r="N28" s="110"/>
+      <c r="O28" s="136" t="n">
         <v>45968</v>
       </c>
-      <c r="P28" s="97" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="n">
+      <c r="P28" s="121" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="104" t="n">
         <v>23</v>
       </c>
-      <c r="B29" s="95" t="s">
+      <c r="B29" s="105" t="s">
         <v>384</v>
       </c>
-      <c r="C29" s="106" t="n">
+      <c r="C29" s="97" t="n">
         <v>713985999</v>
       </c>
-      <c r="D29" s="24" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E29" s="22"/>
-      <c r="F29" s="23" t="n">
+      <c r="D29" s="107" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E29" s="108"/>
+      <c r="F29" s="109" t="n">
         <v>750</v>
       </c>
-      <c r="G29" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="93" t="n">
-        <v>11000</v>
-      </c>
-      <c r="K29" s="22"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="84" t="n">
+      <c r="G29" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H29" s="107"/>
+      <c r="I29" s="107"/>
+      <c r="J29" s="118" t="n">
+        <v>11000</v>
+      </c>
+      <c r="K29" s="108"/>
+      <c r="L29" s="93"/>
+      <c r="M29" s="93"/>
+      <c r="N29" s="93"/>
+      <c r="O29" s="102" t="n">
         <v>45784</v>
       </c>
-      <c r="P29" s="107" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="54" t="n">
+      <c r="P29" s="137" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="138" t="n">
         <v>24</v>
       </c>
-      <c r="B30" s="99" t="s">
-        <v>413</v>
-      </c>
-      <c r="C30" s="96" t="n">
+      <c r="B30" s="96" t="s">
+        <v>415</v>
+      </c>
+      <c r="C30" s="120" t="n">
         <v>717334827</v>
       </c>
-      <c r="D30" s="57" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E30" s="55"/>
-      <c r="F30" s="56" t="n">
+      <c r="D30" s="139" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E30" s="140"/>
+      <c r="F30" s="141" t="n">
         <v>6250</v>
       </c>
-      <c r="G30" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="93" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K30" s="55"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="84" t="n">
+      <c r="G30" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H30" s="139"/>
+      <c r="I30" s="139"/>
+      <c r="J30" s="118" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K30" s="140"/>
+      <c r="L30" s="93"/>
+      <c r="M30" s="93"/>
+      <c r="N30" s="93"/>
+      <c r="O30" s="102" t="n">
         <v>45845</v>
       </c>
-      <c r="P30" s="108" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="109" t="n">
+      <c r="P30" s="142" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="143" t="n">
         <v>25</v>
       </c>
-      <c r="B31" s="110" t="s">
+      <c r="B31" s="144" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="111" t="n">
+      <c r="C31" s="145" t="n">
         <v>712298540</v>
       </c>
-      <c r="D31" s="61" t="n">
+      <c r="D31" s="146" t="n">
         <v>12000</v>
       </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="62" t="n">
+      <c r="E31" s="146"/>
+      <c r="F31" s="147" t="n">
         <v>17750</v>
       </c>
-      <c r="G31" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="93"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="84"/>
-      <c r="P31" s="97"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="109" t="n">
+      <c r="G31" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H31" s="146"/>
+      <c r="I31" s="146"/>
+      <c r="J31" s="118"/>
+      <c r="K31" s="146"/>
+      <c r="L31" s="93"/>
+      <c r="M31" s="93"/>
+      <c r="N31" s="93"/>
+      <c r="O31" s="102"/>
+      <c r="P31" s="121"/>
+    </row>
+    <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="143" t="n">
         <v>26</v>
       </c>
-      <c r="B32" s="99" t="s">
+      <c r="B32" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="111" t="n">
+      <c r="C32" s="145" t="n">
         <v>114717120</v>
       </c>
-      <c r="D32" s="61" t="n">
+      <c r="D32" s="146" t="n">
         <v>12000</v>
       </c>
-      <c r="E32" s="61" t="n">
+      <c r="E32" s="146" t="n">
         <v>12000</v>
       </c>
-      <c r="F32" s="62"/>
-      <c r="G32" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="93"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="84"/>
-      <c r="P32" s="97"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="109" t="n">
+      <c r="F32" s="147"/>
+      <c r="G32" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H32" s="146"/>
+      <c r="I32" s="146"/>
+      <c r="J32" s="118"/>
+      <c r="K32" s="146"/>
+      <c r="L32" s="93"/>
+      <c r="M32" s="93"/>
+      <c r="N32" s="93"/>
+      <c r="O32" s="102"/>
+      <c r="P32" s="121"/>
+    </row>
+    <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="143" t="n">
         <v>27</v>
       </c>
-      <c r="B33" s="112" t="s">
-        <v>415</v>
-      </c>
-      <c r="C33" s="113" t="s">
-        <v>416</v>
-      </c>
-      <c r="D33" s="61" t="n">
+      <c r="B33" s="148" t="s">
+        <v>417</v>
+      </c>
+      <c r="C33" s="149" t="s">
+        <v>418</v>
+      </c>
+      <c r="D33" s="146" t="n">
         <v>12000</v>
       </c>
-      <c r="E33" s="61"/>
-      <c r="F33" s="62"/>
-      <c r="G33" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H33" s="61"/>
-      <c r="I33" s="61"/>
-      <c r="J33" s="93"/>
-      <c r="K33" s="61"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="84"/>
-      <c r="P33" s="107"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="109" t="n">
+      <c r="E33" s="146"/>
+      <c r="F33" s="147"/>
+      <c r="G33" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H33" s="146"/>
+      <c r="I33" s="146"/>
+      <c r="J33" s="118"/>
+      <c r="K33" s="146"/>
+      <c r="L33" s="93"/>
+      <c r="M33" s="93"/>
+      <c r="N33" s="93"/>
+      <c r="O33" s="102"/>
+      <c r="P33" s="137"/>
+    </row>
+    <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="143" t="n">
         <v>28</v>
       </c>
-      <c r="B34" s="110" t="s">
+      <c r="B34" s="144" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="111" t="n">
+      <c r="C34" s="145" t="n">
         <v>713597010</v>
       </c>
-      <c r="D34" s="61" t="n">
+      <c r="D34" s="146" t="n">
         <v>12000</v>
       </c>
-      <c r="E34" s="61"/>
-      <c r="F34" s="62" t="n">
+      <c r="E34" s="146"/>
+      <c r="F34" s="147" t="n">
         <v>19500</v>
       </c>
-      <c r="G34" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="93"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="65"/>
-      <c r="N34" s="66"/>
-      <c r="O34" s="84"/>
-      <c r="P34" s="97"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="109" t="n">
+      <c r="G34" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H34" s="146"/>
+      <c r="I34" s="146"/>
+      <c r="J34" s="118" t="s">
+        <v>419</v>
+      </c>
+      <c r="K34" s="146"/>
+      <c r="L34" s="150"/>
+      <c r="N34" s="151"/>
+      <c r="O34" s="102" t="s">
+        <v>420</v>
+      </c>
+      <c r="P34" s="121" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="143" t="n">
         <v>29</v>
       </c>
-      <c r="B35" s="110" t="s">
+      <c r="B35" s="144" t="s">
         <v>388</v>
       </c>
-      <c r="C35" s="111" t="n">
+      <c r="C35" s="145" t="n">
         <v>726516413</v>
       </c>
-      <c r="D35" s="61" t="n">
+      <c r="D35" s="146" t="n">
         <v>12000</v>
       </c>
-      <c r="E35" s="61"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H35" s="61"/>
-      <c r="I35" s="61"/>
-      <c r="J35" s="93"/>
-      <c r="K35" s="61"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="67"/>
-      <c r="P35" s="101"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="109" t="n">
+      <c r="E35" s="146"/>
+      <c r="F35" s="147"/>
+      <c r="G35" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H35" s="146"/>
+      <c r="I35" s="146"/>
+      <c r="J35" s="118"/>
+      <c r="K35" s="146"/>
+      <c r="L35" s="93"/>
+      <c r="M35" s="93"/>
+      <c r="N35" s="93"/>
+      <c r="O35" s="136"/>
+      <c r="P35" s="126"/>
+    </row>
+    <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="143" t="n">
         <v>30</v>
       </c>
-      <c r="B36" s="110" t="s">
+      <c r="B36" s="144" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="113" t="n">
+      <c r="C36" s="149" t="n">
         <v>713171316</v>
       </c>
-      <c r="D36" s="61" t="n">
+      <c r="D36" s="146" t="n">
         <v>12000</v>
       </c>
-      <c r="E36" s="61"/>
-      <c r="F36" s="62" t="n">
+      <c r="E36" s="146"/>
+      <c r="F36" s="147" t="n">
         <v>12000</v>
       </c>
-      <c r="G36" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H36" s="61"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="114" t="n">
+      <c r="G36" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H36" s="146"/>
+      <c r="I36" s="146"/>
+      <c r="J36" s="152" t="n">
         <v>12250</v>
       </c>
-      <c r="K36" s="61"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="85" t="s">
+      <c r="K36" s="146"/>
+      <c r="L36" s="93"/>
+      <c r="M36" s="93"/>
+      <c r="N36" s="93"/>
+      <c r="O36" s="122" t="s">
+        <v>422</v>
+      </c>
+      <c r="P36" s="121" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="103" t="n">
+        <v>31</v>
+      </c>
+      <c r="B37" s="96" t="s">
+        <v>424</v>
+      </c>
+      <c r="C37" s="125" t="s">
         <v>417</v>
       </c>
-      <c r="P36" s="97" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="68" t="n">
-        <v>31</v>
-      </c>
-      <c r="B37" s="87" t="s">
-        <v>419</v>
-      </c>
-      <c r="C37" s="115" t="s">
-        <v>415</v>
-      </c>
-      <c r="D37" s="18" t="n">
+      <c r="D37" s="103" t="n">
         <v>12000</v>
       </c>
-      <c r="E37" s="18"/>
-      <c r="F37" s="116" t="n">
+      <c r="E37" s="103"/>
+      <c r="F37" s="153" t="n">
         <v>12250</v>
       </c>
-      <c r="G37" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="93" t="n">
+      <c r="G37" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H37" s="103"/>
+      <c r="I37" s="103"/>
+      <c r="J37" s="118" t="n">
         <v>12250</v>
       </c>
-      <c r="K37" s="13"/>
-      <c r="L37" s="69"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="84" t="n">
+      <c r="K37" s="89"/>
+      <c r="L37" s="153"/>
+      <c r="M37" s="89"/>
+      <c r="N37" s="89"/>
+      <c r="O37" s="102" t="n">
         <v>45876</v>
       </c>
-      <c r="P37" s="97" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="n">
+      <c r="P37" s="121" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="103" t="n">
         <v>32</v>
       </c>
-      <c r="B38" s="99" t="s">
-        <v>419</v>
-      </c>
-      <c r="C38" s="100" t="n">
+      <c r="B38" s="96" t="s">
+        <v>424</v>
+      </c>
+      <c r="C38" s="125" t="n">
         <v>707653219</v>
       </c>
-      <c r="D38" s="79" t="n">
+      <c r="D38" s="154" t="n">
         <v>11750</v>
       </c>
-      <c r="E38" s="13"/>
-      <c r="F38" s="71"/>
-      <c r="G38" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="114" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="84" t="n">
+      <c r="E38" s="89"/>
+      <c r="F38" s="155"/>
+      <c r="G38" s="99" t="n">
+        <v>250</v>
+      </c>
+      <c r="H38" s="103"/>
+      <c r="I38" s="103"/>
+      <c r="J38" s="152" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K38" s="89"/>
+      <c r="L38" s="89"/>
+      <c r="M38" s="89"/>
+      <c r="N38" s="89"/>
+      <c r="O38" s="102" t="n">
         <v>45695</v>
       </c>
-      <c r="P38" s="97" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="72"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="74" t="n">
+      <c r="P38" s="121" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="89"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="154"/>
+      <c r="D39" s="156"/>
+      <c r="E39" s="157" t="n">
         <v>12000</v>
       </c>
-      <c r="F39" s="74"/>
-      <c r="G39" s="74" t="n">
+      <c r="F39" s="157"/>
+      <c r="G39" s="157" t="n">
         <v>8000</v>
       </c>
-      <c r="H39" s="74"/>
-      <c r="I39" s="74"/>
-      <c r="J39" s="79"/>
-      <c r="K39" s="74"/>
-      <c r="L39" s="74"/>
-      <c r="M39" s="74"/>
-      <c r="N39" s="74"/>
-      <c r="O39" s="75"/>
-      <c r="P39" s="5"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="76" t="s">
+      <c r="H39" s="157"/>
+      <c r="I39" s="157"/>
+      <c r="J39" s="154"/>
+      <c r="K39" s="157"/>
+      <c r="L39" s="157"/>
+      <c r="M39" s="157"/>
+      <c r="N39" s="157"/>
+      <c r="O39" s="158"/>
+      <c r="P39" s="89"/>
+    </row>
+    <row r="40" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="159" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="117" t="n">
+      <c r="C40" s="159" t="n">
         <f aca="false">SUM(J8:J38)</f>
-        <v>207300</v>
-      </c>
-      <c r="E40" s="77"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="18" t="s">
+        <v>216800</v>
+      </c>
+      <c r="E40" s="160"/>
+    </row>
+    <row r="41" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="18"/>
-      <c r="D41" s="50"/>
-      <c r="F41" s="78"/>
-      <c r="G41" s="78"/>
-      <c r="H41" s="78"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="18"/>
-      <c r="C42" s="79"/>
-      <c r="F42" s="78"/>
-      <c r="G42" s="78"/>
-      <c r="H42" s="78"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="50" t="s">
+      <c r="C41" s="103"/>
+      <c r="D41" s="111"/>
+      <c r="F41" s="161"/>
+      <c r="G41" s="161"/>
+      <c r="H41" s="161"/>
+    </row>
+    <row r="42" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="103"/>
+      <c r="C42" s="154"/>
+      <c r="F42" s="161"/>
+      <c r="G42" s="161"/>
+      <c r="H42" s="161"/>
+    </row>
+    <row r="43" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="118"/>
-      <c r="F43" s="78"/>
-      <c r="G43" s="78"/>
-      <c r="H43" s="78"/>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="68"/>
-      <c r="C44" s="68"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="18" t="s">
-        <v>422</v>
-      </c>
-      <c r="C45" s="68"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="18" t="s">
+      <c r="C43" s="162"/>
+      <c r="F43" s="161"/>
+      <c r="G43" s="161"/>
+      <c r="H43" s="161"/>
+    </row>
+    <row r="44" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="103"/>
+      <c r="C44" s="103"/>
+    </row>
+    <row r="45" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="103" t="s">
+        <v>427</v>
+      </c>
+      <c r="C45" s="103"/>
+    </row>
+    <row r="46" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="68"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="18" t="s">
+      <c r="C46" s="103"/>
+    </row>
+    <row r="47" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="C47" s="68"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="18" t="s">
+      <c r="C47" s="103"/>
+    </row>
+    <row r="48" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="C48" s="68"/>
+      <c r="C48" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/PROPERTIES/QYOTA/QYOTA 2025.xlsx
+++ b/PROPERTIES/QYOTA/QYOTA 2025.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="434">
   <si>
     <t xml:space="preserve">COURTLAND REALTORS LTD P.O.BOX 11993, NAIROBI</t>
   </si>
@@ -1222,12 +1222,21 @@
     <t xml:space="preserve">PRE-PAYMENT</t>
   </si>
   <si>
+    <t xml:space="preserve">16/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGG17ZYY7T</t>
+  </si>
+  <si>
     <t xml:space="preserve">TG32I30ZOC</t>
   </si>
   <si>
     <t xml:space="preserve">TG37F6EEQH</t>
   </si>
   <si>
+    <t xml:space="preserve">GB6LDRT7Y</t>
+  </si>
+  <si>
     <t xml:space="preserve">21/07/2025</t>
   </si>
   <si>
@@ -1282,28 +1291,37 @@
     <t xml:space="preserve">TG76155CIA</t>
   </si>
   <si>
+    <t xml:space="preserve">TGC6PMX1D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VACATING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‘0700481989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGK9TW8MVR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/06/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFU4YKP23A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGE3X44IB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYLVIA MURULE</t>
+  </si>
+  <si>
     <t xml:space="preserve">????</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‘0700481989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,0000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/07/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TGK9TW8MVR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/07/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TGE3X44IB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYLVIA MURULE</t>
   </si>
   <si>
     <t xml:space="preserve">FTX25183LDNVK</t>
@@ -1328,7 +1346,7 @@
     <numFmt numFmtId="169" formatCode="#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1511,6 +1529,21 @@
     <font>
       <b val="true"/>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
       <color rgb="FF00A933"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1525,10 +1558,17 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
+      <sz val="12"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Georgia"/>
+      <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1582,7 +1622,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1593,6 +1633,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFC00000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1661,7 +1707,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="174">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2010,10 +2056,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2066,16 +2108,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2106,8 +2148,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2134,11 +2176,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2146,12 +2188,44 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2166,19 +2240,23 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="26" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="28" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="29" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2186,19 +2264,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="24" fillId="2" borderId="4" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2207,10 +2281,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="29" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2230,35 +2304,35 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="31" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="34" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2266,11 +2340,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2282,7 +2364,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2291,6 +2373,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2306,7 +2392,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4094,18 +4184,18 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="87" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="88" width="29.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="88" width="27.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="88" width="20.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="87" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="87" width="27.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="87" width="20.97"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="5" style="87" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="88" width="19.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="88" width="17.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="87" width="19.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="87" width="17.23"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="10" style="87" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="88" width="21.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="87" width="21.32"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="13" style="87" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="88" width="26.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="15" style="87" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="88" width="21.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="87" width="18.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="87" width="22.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="87" width="21.56"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="87" width="11.53"/>
   </cols>
   <sheetData>
@@ -4130,7 +4220,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="3"/>
-      <c r="P2" s="88" t="s">
+      <c r="P2" s="87" t="s">
         <v>2</v>
       </c>
     </row>
@@ -4144,13 +4234,13 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="3"/>
-      <c r="P3" s="88" t="s">
+      <c r="P3" s="87" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="89"/>
-      <c r="B4" s="89"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="88"/>
       <c r="C4" s="6" t="s">
         <v>5</v>
       </c>
@@ -4160,1214 +4250,1242 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="89"/>
-      <c r="O4" s="89"/>
-      <c r="P4" s="89"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
     </row>
     <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="90"/>
-      <c r="B5" s="90"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="92" t="s">
+      <c r="A5" s="89"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="92"/>
-      <c r="J5" s="91"/>
-      <c r="K5" s="91"/>
-      <c r="L5" s="93"/>
-      <c r="M5" s="93"/>
-      <c r="N5" s="93"/>
-      <c r="O5" s="93"/>
-      <c r="P5" s="93"/>
-    </row>
-    <row r="6" customFormat="false" ht="29.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="90" t="s">
+      <c r="I5" s="91"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="92"/>
+      <c r="M5" s="92"/>
+      <c r="N5" s="92"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="92"/>
+    </row>
+    <row r="6" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="90" t="s">
+      <c r="C6" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="92" t="s">
+      <c r="D6" s="91" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="92" t="s">
+      <c r="E6" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="94" t="s">
+      <c r="F6" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="92" t="s">
+      <c r="G6" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="92" t="s">
+      <c r="H6" s="91" t="s">
         <v>395</v>
       </c>
-      <c r="I6" s="92" t="s">
+      <c r="I6" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="95" t="s">
+      <c r="J6" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="95" t="s">
+      <c r="K6" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="91" t="s">
+      <c r="L6" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="91" t="s">
+      <c r="M6" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="N6" s="91" t="s">
+      <c r="N6" s="90" t="s">
         <v>396</v>
       </c>
-      <c r="O6" s="91" t="s">
+      <c r="O6" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="89" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="89" t="n">
+      <c r="A7" s="88" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="97" t="n">
+      <c r="C7" s="96" t="n">
         <v>703485579</v>
       </c>
-      <c r="D7" s="98" t="n">
+      <c r="D7" s="97" t="n">
         <v>10000</v>
       </c>
-      <c r="E7" s="99"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="101"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="89"/>
-      <c r="M7" s="89"/>
-      <c r="N7" s="89"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="103"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="100" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K7" s="98"/>
+      <c r="L7" s="88"/>
+      <c r="M7" s="88"/>
+      <c r="N7" s="88"/>
+      <c r="O7" s="101" t="s">
+        <v>397</v>
+      </c>
+      <c r="P7" s="102" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="104" t="n">
+      <c r="A8" s="103" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="105" t="s">
+      <c r="B8" s="104" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="106" t="n">
+      <c r="C8" s="105" t="n">
         <v>726646115</v>
       </c>
-      <c r="D8" s="107" t="n">
+      <c r="D8" s="106" t="n">
         <v>10000</v>
       </c>
-      <c r="E8" s="108"/>
-      <c r="F8" s="109" t="n">
+      <c r="E8" s="107"/>
+      <c r="F8" s="108" t="n">
         <v>10750</v>
       </c>
-      <c r="G8" s="108" t="n">
-        <v>250</v>
-      </c>
-      <c r="H8" s="107"/>
-      <c r="I8" s="107"/>
-      <c r="J8" s="89"/>
-      <c r="K8" s="108"/>
-      <c r="L8" s="110"/>
-      <c r="M8" s="110"/>
-      <c r="N8" s="110"/>
-      <c r="O8" s="102"/>
-      <c r="P8" s="111"/>
+      <c r="G8" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H8" s="106"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="107"/>
+      <c r="L8" s="109"/>
+      <c r="M8" s="109"/>
+      <c r="N8" s="109"/>
+      <c r="O8" s="101"/>
+      <c r="P8" s="110"/>
     </row>
     <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="112" t="n">
+      <c r="A9" s="111" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="113" t="s">
+      <c r="B9" s="112" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="114" t="n">
+      <c r="C9" s="113" t="n">
         <v>725840501</v>
       </c>
-      <c r="D9" s="115" t="n">
+      <c r="D9" s="114" t="n">
         <v>10000</v>
       </c>
-      <c r="E9" s="116"/>
-      <c r="F9" s="117" t="n">
-        <v>250</v>
-      </c>
-      <c r="G9" s="108" t="n">
-        <v>250</v>
-      </c>
-      <c r="H9" s="115"/>
-      <c r="I9" s="115"/>
-      <c r="J9" s="118" t="n">
+      <c r="E9" s="115"/>
+      <c r="F9" s="116" t="n">
+        <v>250</v>
+      </c>
+      <c r="G9" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H9" s="114"/>
+      <c r="I9" s="114"/>
+      <c r="J9" s="117" t="n">
         <v>10250</v>
       </c>
-      <c r="K9" s="116"/>
-      <c r="L9" s="110"/>
-      <c r="M9" s="110"/>
-      <c r="N9" s="110"/>
-      <c r="O9" s="102" t="n">
+      <c r="K9" s="115"/>
+      <c r="L9" s="109"/>
+      <c r="M9" s="109"/>
+      <c r="N9" s="109"/>
+      <c r="O9" s="101" t="n">
         <v>45723</v>
       </c>
-      <c r="P9" s="119" t="s">
-        <v>397</v>
+      <c r="P9" s="118" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="104" t="n">
+      <c r="A10" s="103" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="105" t="s">
+      <c r="B10" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="120" t="n">
+      <c r="C10" s="119" t="n">
         <v>706082031</v>
       </c>
-      <c r="D10" s="107" t="n">
+      <c r="D10" s="106" t="n">
         <v>10000</v>
       </c>
-      <c r="E10" s="108"/>
-      <c r="F10" s="109"/>
-      <c r="G10" s="108" t="n">
-        <v>250</v>
-      </c>
-      <c r="H10" s="107"/>
-      <c r="I10" s="107"/>
-      <c r="J10" s="118" t="n">
+      <c r="E10" s="107"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H10" s="106"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="117" t="n">
         <v>10750</v>
       </c>
-      <c r="K10" s="108"/>
-      <c r="L10" s="110"/>
-      <c r="M10" s="110"/>
-      <c r="N10" s="110"/>
-      <c r="O10" s="102" t="n">
+      <c r="K10" s="107"/>
+      <c r="L10" s="109"/>
+      <c r="M10" s="109"/>
+      <c r="N10" s="109"/>
+      <c r="O10" s="101" t="n">
         <v>45723</v>
       </c>
-      <c r="P10" s="121" t="s">
-        <v>398</v>
+      <c r="P10" s="102" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="104" t="n">
+      <c r="A11" s="120" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="105" t="s">
+      <c r="B11" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="120"/>
-      <c r="D11" s="107" t="n">
+      <c r="C11" s="122"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="124" t="n">
+        <v>250</v>
+      </c>
+      <c r="H11" s="123"/>
+      <c r="I11" s="123"/>
+      <c r="J11" s="126"/>
+      <c r="K11" s="124"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="127"/>
+      <c r="N11" s="127"/>
+      <c r="O11" s="128"/>
+      <c r="P11" s="129"/>
+    </row>
+    <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="103" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="104" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" s="105" t="n">
+        <v>796721103</v>
+      </c>
+      <c r="D12" s="130" t="n">
+        <v>9500</v>
+      </c>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H12" s="103"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="117" t="n">
+        <v>9500</v>
+      </c>
+      <c r="K12" s="103"/>
+      <c r="L12" s="109"/>
+      <c r="M12" s="109"/>
+      <c r="N12" s="109"/>
+      <c r="O12" s="101" t="n">
+        <v>45968</v>
+      </c>
+      <c r="P12" s="102" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="103" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="104" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="119" t="n">
+        <v>792896940</v>
+      </c>
+      <c r="D13" s="106" t="n">
+        <v>9500</v>
+      </c>
+      <c r="E13" s="107"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H13" s="106"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="117" t="n">
+        <v>9500</v>
+      </c>
+      <c r="K13" s="107"/>
+      <c r="L13" s="109"/>
+      <c r="M13" s="109"/>
+      <c r="N13" s="109"/>
+      <c r="O13" s="101" t="s">
+        <v>402</v>
+      </c>
+      <c r="P13" s="118" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="103" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="131" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="119" t="n">
+        <v>728513304</v>
+      </c>
+      <c r="D14" s="106" t="n">
         <v>10000</v>
       </c>
-      <c r="E11" s="108"/>
-      <c r="F11" s="109"/>
-      <c r="G11" s="108" t="n">
-        <v>250</v>
-      </c>
-      <c r="H11" s="107"/>
-      <c r="I11" s="107"/>
-      <c r="J11" s="118"/>
-      <c r="K11" s="108"/>
-      <c r="L11" s="110"/>
-      <c r="M11" s="110"/>
-      <c r="N11" s="110"/>
-      <c r="O11" s="122"/>
-      <c r="P11" s="121"/>
-    </row>
-    <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="104" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="105" t="s">
-        <v>212</v>
-      </c>
-      <c r="C12" s="106" t="n">
-        <v>796721103</v>
-      </c>
-      <c r="D12" s="123" t="n">
+      <c r="E14" s="107"/>
+      <c r="F14" s="108" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G14" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H14" s="106"/>
+      <c r="I14" s="106"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="107"/>
+      <c r="L14" s="109"/>
+      <c r="M14" s="109"/>
+      <c r="N14" s="109"/>
+      <c r="O14" s="101"/>
+      <c r="P14" s="118"/>
+    </row>
+    <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="88" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="95" t="s">
+        <v>404</v>
+      </c>
+      <c r="C15" s="132" t="n">
+        <v>710621587</v>
+      </c>
+      <c r="D15" s="97" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E15" s="98"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H15" s="97"/>
+      <c r="I15" s="97"/>
+      <c r="J15" s="117" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K15" s="98"/>
+      <c r="L15" s="92"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="92"/>
+      <c r="O15" s="101" t="n">
+        <v>45845</v>
+      </c>
+      <c r="P15" s="133" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="88" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="95" t="s">
+        <v>298</v>
+      </c>
+      <c r="C16" s="132" t="n">
+        <v>768218105</v>
+      </c>
+      <c r="D16" s="97" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E16" s="98"/>
+      <c r="F16" s="99" t="n">
         <v>9500</v>
       </c>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="108" t="n">
-        <v>250</v>
-      </c>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="118"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="110"/>
-      <c r="M12" s="110"/>
-      <c r="N12" s="110"/>
-      <c r="O12" s="102"/>
-      <c r="P12" s="121"/>
-    </row>
-    <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="104" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="105" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="120" t="n">
-        <v>792896940</v>
-      </c>
-      <c r="D13" s="107" t="n">
-        <v>9500</v>
-      </c>
-      <c r="E13" s="108"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="108" t="n">
-        <v>250</v>
-      </c>
-      <c r="H13" s="107"/>
-      <c r="I13" s="107"/>
-      <c r="J13" s="118" t="n">
-        <v>9500</v>
-      </c>
-      <c r="K13" s="108"/>
-      <c r="L13" s="110"/>
-      <c r="M13" s="110"/>
-      <c r="N13" s="110"/>
-      <c r="O13" s="102" t="s">
-        <v>399</v>
-      </c>
-      <c r="P13" s="119" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="104" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="124" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="120" t="n">
-        <v>728513304</v>
-      </c>
-      <c r="D14" s="107" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E14" s="108"/>
-      <c r="F14" s="109" t="n">
+      <c r="G16" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H16" s="97"/>
+      <c r="I16" s="97"/>
+      <c r="J16" s="117" t="n">
         <v>10500</v>
       </c>
-      <c r="G14" s="108" t="n">
-        <v>250</v>
-      </c>
-      <c r="H14" s="107"/>
-      <c r="I14" s="107"/>
-      <c r="J14" s="118"/>
-      <c r="K14" s="108"/>
-      <c r="L14" s="110"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="102"/>
-      <c r="P14" s="119"/>
-    </row>
-    <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="89" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="96" t="s">
-        <v>401</v>
-      </c>
-      <c r="C15" s="125" t="n">
-        <v>710621587</v>
-      </c>
-      <c r="D15" s="98" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E15" s="99"/>
-      <c r="F15" s="100"/>
-      <c r="G15" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H15" s="98"/>
-      <c r="I15" s="98"/>
-      <c r="J15" s="118" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K15" s="99"/>
-      <c r="L15" s="93"/>
-      <c r="M15" s="93"/>
-      <c r="N15" s="93"/>
-      <c r="O15" s="102" t="n">
+      <c r="K16" s="98"/>
+      <c r="L16" s="134"/>
+      <c r="M16" s="92"/>
+      <c r="N16" s="92"/>
+      <c r="O16" s="101" t="n">
+        <v>-648086</v>
+      </c>
+      <c r="P16" s="102" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="103" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="104" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="119" t="n">
+        <v>703706971</v>
+      </c>
+      <c r="D17" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E17" s="107"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H17" s="106"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="117" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K17" s="107"/>
+      <c r="L17" s="109"/>
+      <c r="M17" s="109"/>
+      <c r="N17" s="109"/>
+      <c r="O17" s="101" t="n">
+        <v>45784</v>
+      </c>
+      <c r="P17" s="118" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="103" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="104" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="119" t="n">
+        <v>727026360</v>
+      </c>
+      <c r="D18" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E18" s="107"/>
+      <c r="F18" s="108"/>
+      <c r="G18" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H18" s="106"/>
+      <c r="I18" s="106"/>
+      <c r="J18" s="117" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K18" s="107"/>
+      <c r="L18" s="109"/>
+      <c r="M18" s="109"/>
+      <c r="N18" s="109"/>
+      <c r="O18" s="101" t="n">
+        <v>45876</v>
+      </c>
+      <c r="P18" s="118" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="103" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="104" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="105" t="n">
+        <v>739314188</v>
+      </c>
+      <c r="D19" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E19" s="107"/>
+      <c r="F19" s="108" t="n">
+        <v>41500</v>
+      </c>
+      <c r="G19" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H19" s="106"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="107"/>
+      <c r="L19" s="135"/>
+      <c r="M19" s="109"/>
+      <c r="N19" s="109"/>
+      <c r="O19" s="136"/>
+      <c r="P19" s="137"/>
+    </row>
+    <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="103" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="104" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="105" t="n">
+        <v>111236304</v>
+      </c>
+      <c r="D20" s="130" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E20" s="103"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H20" s="138"/>
+      <c r="I20" s="138"/>
+      <c r="J20" s="117" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K20" s="103"/>
+      <c r="L20" s="109"/>
+      <c r="M20" s="109"/>
+      <c r="N20" s="109"/>
+      <c r="O20" s="101" t="n">
+        <v>45784</v>
+      </c>
+      <c r="P20" s="139" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="111" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="112" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="105" t="n">
+        <v>723022756</v>
+      </c>
+      <c r="D21" s="114" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E21" s="115"/>
+      <c r="F21" s="116" t="n">
+        <v>20150</v>
+      </c>
+      <c r="G21" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H21" s="114"/>
+      <c r="I21" s="114"/>
+      <c r="J21" s="117" t="n">
+        <v>17300</v>
+      </c>
+      <c r="K21" s="115"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="101" t="n">
+        <v>45695</v>
+      </c>
+      <c r="P21" s="137" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="103" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="119" t="n">
+        <v>705321457</v>
+      </c>
+      <c r="D22" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E22" s="107"/>
+      <c r="F22" s="108" t="n">
+        <v>11250</v>
+      </c>
+      <c r="G22" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H22" s="106"/>
+      <c r="I22" s="106"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="107"/>
+      <c r="L22" s="109"/>
+      <c r="M22" s="109"/>
+      <c r="N22" s="109"/>
+      <c r="O22" s="101"/>
+      <c r="P22" s="102"/>
+    </row>
+    <row r="23" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="88" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="95" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="132" t="n">
+        <v>726518863</v>
+      </c>
+      <c r="D23" s="97" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E23" s="98"/>
+      <c r="F23" s="99"/>
+      <c r="G23" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H23" s="97"/>
+      <c r="I23" s="97"/>
+      <c r="J23" s="117" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K23" s="98"/>
+      <c r="L23" s="92"/>
+      <c r="M23" s="92"/>
+      <c r="N23" s="92"/>
+      <c r="O23" s="101" t="n">
         <v>45845</v>
       </c>
-      <c r="P15" s="126" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="89" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="96" t="s">
-        <v>298</v>
-      </c>
-      <c r="C16" s="125" t="n">
-        <v>768218105</v>
-      </c>
-      <c r="D16" s="98" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E16" s="99"/>
-      <c r="F16" s="100" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G16" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="118" t="n">
+      <c r="P23" s="110" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="88" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" s="95" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="132" t="n">
+        <v>727516082</v>
+      </c>
+      <c r="D24" s="97" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E24" s="98"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H24" s="97"/>
+      <c r="I24" s="97"/>
+      <c r="J24" s="117" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K24" s="98"/>
+      <c r="L24" s="134"/>
+      <c r="M24" s="92"/>
+      <c r="N24" s="92"/>
+      <c r="O24" s="101" t="n">
+        <v>45754</v>
+      </c>
+      <c r="P24" s="102" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="103" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" s="104" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="119" t="n">
+        <v>706651018</v>
+      </c>
+      <c r="D25" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E25" s="107"/>
+      <c r="F25" s="108" t="n">
+        <v>12050</v>
+      </c>
+      <c r="G25" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H25" s="106"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="117"/>
+      <c r="K25" s="107"/>
+      <c r="L25" s="109"/>
+      <c r="M25" s="109"/>
+      <c r="N25" s="109"/>
+      <c r="O25" s="140"/>
+      <c r="P25" s="118"/>
+    </row>
+    <row r="26" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="88" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" s="95" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="132" t="n">
+        <v>718723801</v>
+      </c>
+      <c r="D26" s="97" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E26" s="98"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H26" s="97"/>
+      <c r="I26" s="97"/>
+      <c r="J26" s="117" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K26" s="98"/>
+      <c r="L26" s="88"/>
+      <c r="M26" s="88"/>
+      <c r="N26" s="88"/>
+      <c r="O26" s="101" t="n">
+        <v>45723</v>
+      </c>
+      <c r="P26" s="141" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="103" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" s="104" t="s">
+        <v>154</v>
+      </c>
+      <c r="C27" s="105" t="n">
+        <v>729400661</v>
+      </c>
+      <c r="D27" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E27" s="107"/>
+      <c r="F27" s="108" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G27" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H27" s="142"/>
+      <c r="I27" s="106"/>
+      <c r="J27" s="117" t="n">
         <v>10500</v>
       </c>
-      <c r="K16" s="99"/>
-      <c r="L16" s="127"/>
-      <c r="M16" s="93"/>
-      <c r="N16" s="93"/>
-      <c r="O16" s="102" t="n">
-        <v>-648086</v>
-      </c>
-      <c r="P16" s="121" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="104" t="n">
+      <c r="K27" s="107"/>
+      <c r="L27" s="109"/>
+      <c r="M27" s="109"/>
+      <c r="N27" s="109"/>
+      <c r="O27" s="101" t="n">
+        <v>45695</v>
+      </c>
+      <c r="P27" s="102" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="103" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" s="104" t="s">
+        <v>415</v>
+      </c>
+      <c r="C28" s="105" t="n">
+        <v>101921686</v>
+      </c>
+      <c r="D28" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E28" s="107"/>
+      <c r="F28" s="108"/>
+      <c r="G28" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H28" s="106"/>
+      <c r="I28" s="106"/>
+      <c r="J28" s="117" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K28" s="107"/>
+      <c r="L28" s="109"/>
+      <c r="M28" s="109"/>
+      <c r="N28" s="109"/>
+      <c r="O28" s="143" t="n">
+        <v>45968</v>
+      </c>
+      <c r="P28" s="102" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="103" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" s="104" t="s">
+        <v>384</v>
+      </c>
+      <c r="C29" s="96" t="n">
+        <v>713985999</v>
+      </c>
+      <c r="D29" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E29" s="107"/>
+      <c r="F29" s="108" t="n">
+        <v>750</v>
+      </c>
+      <c r="G29" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H29" s="106"/>
+      <c r="I29" s="106"/>
+      <c r="J29" s="117" t="n">
+        <v>11000</v>
+      </c>
+      <c r="K29" s="107"/>
+      <c r="L29" s="92"/>
+      <c r="M29" s="92"/>
+      <c r="N29" s="92"/>
+      <c r="O29" s="101" t="n">
+        <v>45784</v>
+      </c>
+      <c r="P29" s="144" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="145" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" s="95" t="s">
+        <v>418</v>
+      </c>
+      <c r="C30" s="119" t="n">
+        <v>717334827</v>
+      </c>
+      <c r="D30" s="146" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E30" s="147"/>
+      <c r="F30" s="148" t="n">
+        <v>6250</v>
+      </c>
+      <c r="G30" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H30" s="146"/>
+      <c r="I30" s="146"/>
+      <c r="J30" s="117" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K30" s="147"/>
+      <c r="L30" s="92"/>
+      <c r="M30" s="92"/>
+      <c r="N30" s="92"/>
+      <c r="O30" s="101" t="n">
+        <v>45845</v>
+      </c>
+      <c r="P30" s="149" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="150" t="n">
+        <v>25</v>
+      </c>
+      <c r="B31" s="151" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="152" t="n">
+        <v>712298540</v>
+      </c>
+      <c r="D31" s="153" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E31" s="153"/>
+      <c r="F31" s="154" t="n">
+        <v>17750</v>
+      </c>
+      <c r="G31" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H31" s="153"/>
+      <c r="I31" s="153"/>
+      <c r="J31" s="117" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K31" s="153"/>
+      <c r="L31" s="92"/>
+      <c r="M31" s="92"/>
+      <c r="N31" s="92"/>
+      <c r="O31" s="101" t="n">
+        <v>45998</v>
+      </c>
+      <c r="P31" s="102" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="150" t="n">
+        <v>26</v>
+      </c>
+      <c r="B32" s="95" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="152" t="n">
+        <v>114717120</v>
+      </c>
+      <c r="D32" s="153" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E32" s="153" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F32" s="154"/>
+      <c r="G32" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H32" s="153"/>
+      <c r="I32" s="153"/>
+      <c r="J32" s="117"/>
+      <c r="K32" s="153"/>
+      <c r="L32" s="92"/>
+      <c r="M32" s="92"/>
+      <c r="N32" s="92"/>
+      <c r="O32" s="101"/>
+      <c r="P32" s="102"/>
+    </row>
+    <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="150" t="n">
+        <v>27</v>
+      </c>
+      <c r="B33" s="155" t="s">
+        <v>421</v>
+      </c>
+      <c r="C33" s="156" t="s">
+        <v>422</v>
+      </c>
+      <c r="D33" s="153" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E33" s="153"/>
+      <c r="F33" s="154"/>
+      <c r="G33" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H33" s="153"/>
+      <c r="I33" s="153"/>
+      <c r="J33" s="117"/>
+      <c r="K33" s="153"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+      <c r="N33" s="92"/>
+      <c r="O33" s="101"/>
+      <c r="P33" s="144"/>
+    </row>
+    <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="150" t="n">
+        <v>28</v>
+      </c>
+      <c r="B34" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="152" t="n">
+        <v>713597010</v>
+      </c>
+      <c r="D34" s="153" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E34" s="153"/>
+      <c r="F34" s="154" t="n">
+        <v>19500</v>
+      </c>
+      <c r="G34" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H34" s="153"/>
+      <c r="I34" s="153"/>
+      <c r="J34" s="117" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K34" s="153"/>
+      <c r="L34" s="157"/>
+      <c r="N34" s="158"/>
+      <c r="O34" s="101" t="s">
+        <v>423</v>
+      </c>
+      <c r="P34" s="102" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="150" t="n">
+        <v>29</v>
+      </c>
+      <c r="B35" s="151" t="s">
+        <v>388</v>
+      </c>
+      <c r="C35" s="152" t="n">
+        <v>726516413</v>
+      </c>
+      <c r="D35" s="153" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E35" s="153"/>
+      <c r="F35" s="154"/>
+      <c r="G35" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H35" s="153"/>
+      <c r="I35" s="153"/>
+      <c r="J35" s="117" t="n">
+        <v>12500</v>
+      </c>
+      <c r="K35" s="153"/>
+      <c r="L35" s="92"/>
+      <c r="M35" s="92"/>
+      <c r="N35" s="92"/>
+      <c r="O35" s="143" t="s">
+        <v>425</v>
+      </c>
+      <c r="P35" s="159" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="150" t="n">
+        <v>30</v>
+      </c>
+      <c r="B36" s="151" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="156" t="n">
+        <v>713171316</v>
+      </c>
+      <c r="D36" s="153" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E36" s="153"/>
+      <c r="F36" s="154" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G36" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H36" s="153"/>
+      <c r="I36" s="153"/>
+      <c r="J36" s="160" t="n">
+        <v>12250</v>
+      </c>
+      <c r="K36" s="153"/>
+      <c r="L36" s="92"/>
+      <c r="M36" s="92"/>
+      <c r="N36" s="92"/>
+      <c r="O36" s="136" t="s">
+        <v>427</v>
+      </c>
+      <c r="P36" s="102" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="161" t="n">
+        <v>31</v>
+      </c>
+      <c r="B37" s="95" t="s">
+        <v>429</v>
+      </c>
+      <c r="C37" s="132" t="s">
+        <v>430</v>
+      </c>
+      <c r="D37" s="161" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E37" s="161"/>
+      <c r="F37" s="162" t="n">
+        <v>12250</v>
+      </c>
+      <c r="G37" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H37" s="161"/>
+      <c r="I37" s="161"/>
+      <c r="J37" s="117" t="n">
+        <v>12250</v>
+      </c>
+      <c r="K37" s="88"/>
+      <c r="L37" s="162"/>
+      <c r="M37" s="88"/>
+      <c r="N37" s="88"/>
+      <c r="O37" s="101" t="n">
+        <v>45876</v>
+      </c>
+      <c r="P37" s="102" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="161" t="n">
+        <v>32</v>
+      </c>
+      <c r="B38" s="95" t="s">
+        <v>429</v>
+      </c>
+      <c r="C38" s="132" t="n">
+        <v>707653219</v>
+      </c>
+      <c r="D38" s="163" t="n">
+        <v>11750</v>
+      </c>
+      <c r="E38" s="88"/>
+      <c r="F38" s="164"/>
+      <c r="G38" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H38" s="161"/>
+      <c r="I38" s="161"/>
+      <c r="J38" s="160" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K38" s="88"/>
+      <c r="L38" s="88"/>
+      <c r="M38" s="88"/>
+      <c r="N38" s="88"/>
+      <c r="O38" s="101" t="n">
+        <v>45695</v>
+      </c>
+      <c r="P38" s="102" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="88"/>
+      <c r="B39" s="161"/>
+      <c r="C39" s="163"/>
+      <c r="D39" s="165" t="n">
+        <f aca="false">SUM(D7:D38)</f>
+        <v>340750</v>
+      </c>
+      <c r="E39" s="166" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F39" s="166"/>
+      <c r="G39" s="166" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H39" s="166"/>
+      <c r="I39" s="166"/>
+      <c r="J39" s="167" t="n">
+        <f aca="false">SUM(J7:J38)</f>
+        <v>278800</v>
+      </c>
+      <c r="K39" s="166"/>
+      <c r="L39" s="166"/>
+      <c r="M39" s="166"/>
+      <c r="N39" s="166"/>
+      <c r="O39" s="168"/>
+      <c r="P39" s="88"/>
+    </row>
+    <row r="40" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="169" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="169" t="n">
+        <f aca="false">SUM(J8:J38)</f>
+        <v>268800</v>
+      </c>
+      <c r="E40" s="170"/>
+    </row>
+    <row r="41" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="105" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="120" t="n">
-        <v>703706971</v>
-      </c>
-      <c r="D17" s="107" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E17" s="108"/>
-      <c r="F17" s="109"/>
-      <c r="G17" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H17" s="107"/>
-      <c r="I17" s="107"/>
-      <c r="J17" s="118" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K17" s="108"/>
-      <c r="L17" s="110"/>
-      <c r="M17" s="110"/>
-      <c r="N17" s="110"/>
-      <c r="O17" s="102" t="n">
-        <v>45784</v>
-      </c>
-      <c r="P17" s="119" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="104" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="105" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="120" t="n">
-        <v>727026360</v>
-      </c>
-      <c r="D18" s="107" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E18" s="108"/>
-      <c r="F18" s="109"/>
-      <c r="G18" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H18" s="107"/>
-      <c r="I18" s="107"/>
-      <c r="J18" s="118" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K18" s="108"/>
-      <c r="L18" s="110"/>
-      <c r="M18" s="110"/>
-      <c r="N18" s="110"/>
-      <c r="O18" s="102" t="n">
-        <v>45876</v>
-      </c>
-      <c r="P18" s="119" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="104" t="n">
+      <c r="C41" s="161"/>
+      <c r="D41" s="171"/>
+      <c r="F41" s="172"/>
+      <c r="G41" s="172"/>
+      <c r="H41" s="172"/>
+    </row>
+    <row r="42" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="161"/>
+      <c r="C42" s="163"/>
+      <c r="F42" s="172"/>
+      <c r="G42" s="172"/>
+      <c r="H42" s="172"/>
+    </row>
+    <row r="43" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="171" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="173"/>
+      <c r="F43" s="172"/>
+      <c r="G43" s="172"/>
+      <c r="H43" s="172"/>
+    </row>
+    <row r="44" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="161"/>
+      <c r="C44" s="161"/>
+    </row>
+    <row r="45" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="161" t="s">
+        <v>433</v>
+      </c>
+      <c r="C45" s="161"/>
+    </row>
+    <row r="46" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="161" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="105" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="106" t="n">
-        <v>739314188</v>
-      </c>
-      <c r="D19" s="107" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E19" s="108"/>
-      <c r="F19" s="109" t="n">
-        <v>41500</v>
-      </c>
-      <c r="G19" s="108" t="n">
-        <v>250</v>
-      </c>
-      <c r="H19" s="107"/>
-      <c r="I19" s="107"/>
-      <c r="J19" s="118"/>
-      <c r="K19" s="108"/>
-      <c r="L19" s="128"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="122"/>
-      <c r="P19" s="129"/>
-    </row>
-    <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="104" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" s="105" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="106" t="n">
-        <v>111236304</v>
-      </c>
-      <c r="D20" s="123" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E20" s="104"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="108" t="n">
-        <v>250</v>
-      </c>
-      <c r="H20" s="130"/>
-      <c r="I20" s="130"/>
-      <c r="J20" s="118" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K20" s="104"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="102" t="n">
-        <v>45784</v>
-      </c>
-      <c r="P20" s="131" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="112" t="n">
-        <v>15</v>
-      </c>
-      <c r="B21" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="106" t="n">
-        <v>723022756</v>
-      </c>
-      <c r="D21" s="115" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E21" s="116"/>
-      <c r="F21" s="117" t="n">
-        <v>20150</v>
-      </c>
-      <c r="G21" s="108" t="n">
-        <v>250</v>
-      </c>
-      <c r="H21" s="115"/>
-      <c r="I21" s="115"/>
-      <c r="J21" s="118" t="n">
-        <v>17300</v>
-      </c>
-      <c r="K21" s="116"/>
-      <c r="L21" s="110"/>
-      <c r="M21" s="110"/>
-      <c r="N21" s="110"/>
-      <c r="O21" s="102" t="n">
-        <v>45695</v>
-      </c>
-      <c r="P21" s="129" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="104" t="n">
-        <v>16</v>
-      </c>
-      <c r="B22" s="105" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="120" t="n">
-        <v>705321457</v>
-      </c>
-      <c r="D22" s="107" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E22" s="108"/>
-      <c r="F22" s="109" t="n">
-        <v>11250</v>
-      </c>
-      <c r="G22" s="108" t="n">
-        <v>250</v>
-      </c>
-      <c r="H22" s="107"/>
-      <c r="I22" s="107"/>
-      <c r="J22" s="118"/>
-      <c r="K22" s="108"/>
-      <c r="L22" s="110"/>
-      <c r="M22" s="110"/>
-      <c r="N22" s="110"/>
-      <c r="O22" s="102"/>
-      <c r="P22" s="121"/>
-    </row>
-    <row r="23" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="89" t="n">
-        <v>17</v>
-      </c>
-      <c r="B23" s="96" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="125" t="n">
-        <v>726518863</v>
-      </c>
-      <c r="D23" s="98" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E23" s="99"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H23" s="98"/>
-      <c r="I23" s="98"/>
-      <c r="J23" s="118" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K23" s="99"/>
-      <c r="L23" s="93"/>
-      <c r="M23" s="93"/>
-      <c r="N23" s="93"/>
-      <c r="O23" s="102" t="n">
-        <v>45845</v>
-      </c>
-      <c r="P23" s="132" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="89" t="n">
-        <v>18</v>
-      </c>
-      <c r="B24" s="96" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="125" t="n">
-        <v>727516082</v>
-      </c>
-      <c r="D24" s="98" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E24" s="99"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H24" s="98"/>
-      <c r="I24" s="98"/>
-      <c r="J24" s="118" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K24" s="99"/>
-      <c r="L24" s="127"/>
-      <c r="M24" s="93"/>
-      <c r="N24" s="93"/>
-      <c r="O24" s="102" t="n">
-        <v>45754</v>
-      </c>
-      <c r="P24" s="121" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="104" t="n">
-        <v>19</v>
-      </c>
-      <c r="B25" s="105" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" s="120" t="n">
-        <v>706651018</v>
-      </c>
-      <c r="D25" s="107" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E25" s="108"/>
-      <c r="F25" s="109" t="n">
-        <v>12050</v>
-      </c>
-      <c r="G25" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H25" s="107"/>
-      <c r="I25" s="107"/>
-      <c r="J25" s="118"/>
-      <c r="K25" s="108"/>
-      <c r="L25" s="110"/>
-      <c r="M25" s="110"/>
-      <c r="N25" s="110"/>
-      <c r="O25" s="133"/>
-      <c r="P25" s="119"/>
-    </row>
-    <row r="26" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="89" t="n">
-        <v>20</v>
-      </c>
-      <c r="B26" s="96" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="125" t="n">
-        <v>718723801</v>
-      </c>
-      <c r="D26" s="98" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E26" s="99"/>
-      <c r="F26" s="100"/>
-      <c r="G26" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H26" s="98"/>
-      <c r="I26" s="98"/>
-      <c r="J26" s="118" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K26" s="99"/>
-      <c r="L26" s="89"/>
-      <c r="M26" s="89"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="102" t="n">
-        <v>45723</v>
-      </c>
-      <c r="P26" s="134" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="104" t="n">
-        <v>21</v>
-      </c>
-      <c r="B27" s="105" t="s">
-        <v>154</v>
-      </c>
-      <c r="C27" s="106" t="n">
-        <v>729400661</v>
-      </c>
-      <c r="D27" s="107" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E27" s="108"/>
-      <c r="F27" s="109" t="n">
-        <v>1750</v>
-      </c>
-      <c r="G27" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H27" s="135"/>
-      <c r="I27" s="107"/>
-      <c r="J27" s="118" t="n">
-        <v>10500</v>
-      </c>
-      <c r="K27" s="108"/>
-      <c r="L27" s="110"/>
-      <c r="M27" s="110"/>
-      <c r="N27" s="110"/>
-      <c r="O27" s="102" t="n">
-        <v>45695</v>
-      </c>
-      <c r="P27" s="121" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="104" t="n">
-        <v>22</v>
-      </c>
-      <c r="B28" s="105" t="s">
-        <v>412</v>
-      </c>
-      <c r="C28" s="106" t="n">
-        <v>101921686</v>
-      </c>
-      <c r="D28" s="107" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E28" s="108"/>
-      <c r="F28" s="109"/>
-      <c r="G28" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H28" s="107"/>
-      <c r="I28" s="107"/>
-      <c r="J28" s="118" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K28" s="108"/>
-      <c r="L28" s="110"/>
-      <c r="M28" s="110"/>
-      <c r="N28" s="110"/>
-      <c r="O28" s="136" t="n">
-        <v>45968</v>
-      </c>
-      <c r="P28" s="121" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="104" t="n">
-        <v>23</v>
-      </c>
-      <c r="B29" s="105" t="s">
-        <v>384</v>
-      </c>
-      <c r="C29" s="97" t="n">
-        <v>713985999</v>
-      </c>
-      <c r="D29" s="107" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E29" s="108"/>
-      <c r="F29" s="109" t="n">
-        <v>750</v>
-      </c>
-      <c r="G29" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H29" s="107"/>
-      <c r="I29" s="107"/>
-      <c r="J29" s="118" t="n">
-        <v>11000</v>
-      </c>
-      <c r="K29" s="108"/>
-      <c r="L29" s="93"/>
-      <c r="M29" s="93"/>
-      <c r="N29" s="93"/>
-      <c r="O29" s="102" t="n">
-        <v>45784</v>
-      </c>
-      <c r="P29" s="137" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="138" t="n">
-        <v>24</v>
-      </c>
-      <c r="B30" s="96" t="s">
-        <v>415</v>
-      </c>
-      <c r="C30" s="120" t="n">
-        <v>717334827</v>
-      </c>
-      <c r="D30" s="139" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E30" s="140"/>
-      <c r="F30" s="141" t="n">
-        <v>6250</v>
-      </c>
-      <c r="G30" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H30" s="139"/>
-      <c r="I30" s="139"/>
-      <c r="J30" s="118" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K30" s="140"/>
-      <c r="L30" s="93"/>
-      <c r="M30" s="93"/>
-      <c r="N30" s="93"/>
-      <c r="O30" s="102" t="n">
-        <v>45845</v>
-      </c>
-      <c r="P30" s="142" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="143" t="n">
-        <v>25</v>
-      </c>
-      <c r="B31" s="144" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="145" t="n">
-        <v>712298540</v>
-      </c>
-      <c r="D31" s="146" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E31" s="146"/>
-      <c r="F31" s="147" t="n">
-        <v>17750</v>
-      </c>
-      <c r="G31" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H31" s="146"/>
-      <c r="I31" s="146"/>
-      <c r="J31" s="118"/>
-      <c r="K31" s="146"/>
-      <c r="L31" s="93"/>
-      <c r="M31" s="93"/>
-      <c r="N31" s="93"/>
-      <c r="O31" s="102"/>
-      <c r="P31" s="121"/>
-    </row>
-    <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="143" t="n">
-        <v>26</v>
-      </c>
-      <c r="B32" s="96" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="145" t="n">
-        <v>114717120</v>
-      </c>
-      <c r="D32" s="146" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E32" s="146" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F32" s="147"/>
-      <c r="G32" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H32" s="146"/>
-      <c r="I32" s="146"/>
-      <c r="J32" s="118"/>
-      <c r="K32" s="146"/>
-      <c r="L32" s="93"/>
-      <c r="M32" s="93"/>
-      <c r="N32" s="93"/>
-      <c r="O32" s="102"/>
-      <c r="P32" s="121"/>
-    </row>
-    <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="143" t="n">
-        <v>27</v>
-      </c>
-      <c r="B33" s="148" t="s">
-        <v>417</v>
-      </c>
-      <c r="C33" s="149" t="s">
-        <v>418</v>
-      </c>
-      <c r="D33" s="146" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E33" s="146"/>
-      <c r="F33" s="147"/>
-      <c r="G33" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H33" s="146"/>
-      <c r="I33" s="146"/>
-      <c r="J33" s="118"/>
-      <c r="K33" s="146"/>
-      <c r="L33" s="93"/>
-      <c r="M33" s="93"/>
-      <c r="N33" s="93"/>
-      <c r="O33" s="102"/>
-      <c r="P33" s="137"/>
-    </row>
-    <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="143" t="n">
-        <v>28</v>
-      </c>
-      <c r="B34" s="144" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" s="145" t="n">
-        <v>713597010</v>
-      </c>
-      <c r="D34" s="146" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E34" s="146"/>
-      <c r="F34" s="147" t="n">
-        <v>19500</v>
-      </c>
-      <c r="G34" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H34" s="146"/>
-      <c r="I34" s="146"/>
-      <c r="J34" s="118" t="s">
-        <v>419</v>
-      </c>
-      <c r="K34" s="146"/>
-      <c r="L34" s="150"/>
-      <c r="N34" s="151"/>
-      <c r="O34" s="102" t="s">
-        <v>420</v>
-      </c>
-      <c r="P34" s="121" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="143" t="n">
-        <v>29</v>
-      </c>
-      <c r="B35" s="144" t="s">
-        <v>388</v>
-      </c>
-      <c r="C35" s="145" t="n">
-        <v>726516413</v>
-      </c>
-      <c r="D35" s="146" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E35" s="146"/>
-      <c r="F35" s="147"/>
-      <c r="G35" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H35" s="146"/>
-      <c r="I35" s="146"/>
-      <c r="J35" s="118"/>
-      <c r="K35" s="146"/>
-      <c r="L35" s="93"/>
-      <c r="M35" s="93"/>
-      <c r="N35" s="93"/>
-      <c r="O35" s="136"/>
-      <c r="P35" s="126"/>
-    </row>
-    <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="143" t="n">
-        <v>30</v>
-      </c>
-      <c r="B36" s="144" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="149" t="n">
-        <v>713171316</v>
-      </c>
-      <c r="D36" s="146" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E36" s="146"/>
-      <c r="F36" s="147" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G36" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H36" s="146"/>
-      <c r="I36" s="146"/>
-      <c r="J36" s="152" t="n">
-        <v>12250</v>
-      </c>
-      <c r="K36" s="146"/>
-      <c r="L36" s="93"/>
-      <c r="M36" s="93"/>
-      <c r="N36" s="93"/>
-      <c r="O36" s="122" t="s">
-        <v>422</v>
-      </c>
-      <c r="P36" s="121" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="103" t="n">
-        <v>31</v>
-      </c>
-      <c r="B37" s="96" t="s">
-        <v>424</v>
-      </c>
-      <c r="C37" s="125" t="s">
-        <v>417</v>
-      </c>
-      <c r="D37" s="103" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E37" s="103"/>
-      <c r="F37" s="153" t="n">
-        <v>12250</v>
-      </c>
-      <c r="G37" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H37" s="103"/>
-      <c r="I37" s="103"/>
-      <c r="J37" s="118" t="n">
-        <v>12250</v>
-      </c>
-      <c r="K37" s="89"/>
-      <c r="L37" s="153"/>
-      <c r="M37" s="89"/>
-      <c r="N37" s="89"/>
-      <c r="O37" s="102" t="n">
-        <v>45876</v>
-      </c>
-      <c r="P37" s="121" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="103" t="n">
-        <v>32</v>
-      </c>
-      <c r="B38" s="96" t="s">
-        <v>424</v>
-      </c>
-      <c r="C38" s="125" t="n">
-        <v>707653219</v>
-      </c>
-      <c r="D38" s="154" t="n">
-        <v>11750</v>
-      </c>
-      <c r="E38" s="89"/>
-      <c r="F38" s="155"/>
-      <c r="G38" s="99" t="n">
-        <v>250</v>
-      </c>
-      <c r="H38" s="103"/>
-      <c r="I38" s="103"/>
-      <c r="J38" s="152" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K38" s="89"/>
-      <c r="L38" s="89"/>
-      <c r="M38" s="89"/>
-      <c r="N38" s="89"/>
-      <c r="O38" s="102" t="n">
-        <v>45695</v>
-      </c>
-      <c r="P38" s="121" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="89"/>
-      <c r="B39" s="103"/>
-      <c r="C39" s="154"/>
-      <c r="D39" s="156"/>
-      <c r="E39" s="157" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F39" s="157"/>
-      <c r="G39" s="157" t="n">
-        <v>8000</v>
-      </c>
-      <c r="H39" s="157"/>
-      <c r="I39" s="157"/>
-      <c r="J39" s="154"/>
-      <c r="K39" s="157"/>
-      <c r="L39" s="157"/>
-      <c r="M39" s="157"/>
-      <c r="N39" s="157"/>
-      <c r="O39" s="158"/>
-      <c r="P39" s="89"/>
-    </row>
-    <row r="40" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="159" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="159" t="n">
-        <f aca="false">SUM(J8:J38)</f>
-        <v>216800</v>
-      </c>
-      <c r="E40" s="160"/>
-    </row>
-    <row r="41" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="103" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="103"/>
-      <c r="D41" s="111"/>
-      <c r="F41" s="161"/>
-      <c r="G41" s="161"/>
-      <c r="H41" s="161"/>
-    </row>
-    <row r="42" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="103"/>
-      <c r="C42" s="154"/>
-      <c r="F42" s="161"/>
-      <c r="G42" s="161"/>
-      <c r="H42" s="161"/>
-    </row>
-    <row r="43" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="111" t="s">
+      <c r="C46" s="161"/>
+    </row>
+    <row r="47" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="161" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" s="161"/>
+    </row>
+    <row r="48" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="161" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="162"/>
-      <c r="F43" s="161"/>
-      <c r="G43" s="161"/>
-      <c r="H43" s="161"/>
-    </row>
-    <row r="44" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="103"/>
-      <c r="C44" s="103"/>
-    </row>
-    <row r="45" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="103" t="s">
-        <v>427</v>
-      </c>
-      <c r="C45" s="103"/>
-    </row>
-    <row r="46" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="103" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" s="103"/>
-    </row>
-    <row r="47" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="103" t="s">
-        <v>89</v>
-      </c>
-      <c r="C47" s="103"/>
-    </row>
-    <row r="48" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="103" t="s">
-        <v>86</v>
-      </c>
-      <c r="C48" s="103"/>
+      <c r="C48" s="161"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/PROPERTIES/QYOTA/QYOTA 2025.xlsx
+++ b/PROPERTIES/QYOTA/QYOTA 2025.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="437">
   <si>
     <t xml:space="preserve">COURTLAND REALTORS LTD P.O.BOX 11993, NAIROBI</t>
   </si>
@@ -1228,6 +1228,12 @@
     <t xml:space="preserve">TGG17ZYY7T</t>
   </si>
   <si>
+    <t xml:space="preserve">24/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGO7ATDJQP</t>
+  </si>
+  <si>
     <t xml:space="preserve">TG32I30ZOC</t>
   </si>
   <si>
@@ -1294,12 +1300,18 @@
     <t xml:space="preserve">TGC6PMX1D2</t>
   </si>
   <si>
-    <t xml:space="preserve">VACATING</t>
+    <t xml:space="preserve">????</t>
   </si>
   <si>
     <t xml:space="preserve">‘0700481989</t>
   </si>
   <si>
+    <t xml:space="preserve">25/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGP9F5MZAH</t>
+  </si>
+  <si>
     <t xml:space="preserve">20/07/2025</t>
   </si>
   <si>
@@ -1319,9 +1331,6 @@
   </si>
   <si>
     <t xml:space="preserve">SYLVIA MURULE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">????</t>
   </si>
   <si>
     <t xml:space="preserve">FTX25183LDNVK</t>
@@ -1346,7 +1355,7 @@
     <numFmt numFmtId="169" formatCode="#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1528,13 +1537,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Georgia"/>
@@ -1707,7 +1709,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="172">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2108,7 +2110,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2116,7 +2118,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2144,11 +2146,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="22" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2176,11 +2182,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2212,7 +2218,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2224,7 +2230,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2240,15 +2246,15 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="25" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="27" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="28" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="27" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2256,7 +2262,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="28" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2264,7 +2270,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2272,7 +2278,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2284,7 +2290,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2304,35 +2310,35 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="30" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="29" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="34" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2340,19 +2346,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2360,11 +2362,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2373,10 +2371,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2396,7 +2390,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4384,48 +4378,54 @@
       </c>
       <c r="H8" s="106"/>
       <c r="I8" s="106"/>
-      <c r="J8" s="88"/>
+      <c r="J8" s="109" t="n">
+        <v>10250</v>
+      </c>
       <c r="K8" s="107"/>
-      <c r="L8" s="109"/>
-      <c r="M8" s="109"/>
-      <c r="N8" s="109"/>
-      <c r="O8" s="101"/>
-      <c r="P8" s="110"/>
+      <c r="L8" s="110"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="110"/>
+      <c r="O8" s="101" t="s">
+        <v>399</v>
+      </c>
+      <c r="P8" s="111" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="111" t="n">
+      <c r="A9" s="112" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="112" t="s">
+      <c r="B9" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="113" t="n">
+      <c r="C9" s="114" t="n">
         <v>725840501</v>
       </c>
-      <c r="D9" s="114" t="n">
+      <c r="D9" s="115" t="n">
         <v>10000</v>
       </c>
-      <c r="E9" s="115"/>
-      <c r="F9" s="116" t="n">
+      <c r="E9" s="116"/>
+      <c r="F9" s="117" t="n">
         <v>250</v>
       </c>
       <c r="G9" s="107" t="n">
         <v>250</v>
       </c>
-      <c r="H9" s="114"/>
-      <c r="I9" s="114"/>
-      <c r="J9" s="117" t="n">
+      <c r="H9" s="115"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="118" t="n">
         <v>10250</v>
       </c>
-      <c r="K9" s="115"/>
-      <c r="L9" s="109"/>
-      <c r="M9" s="109"/>
-      <c r="N9" s="109"/>
+      <c r="K9" s="116"/>
+      <c r="L9" s="110"/>
+      <c r="M9" s="110"/>
+      <c r="N9" s="110"/>
       <c r="O9" s="101" t="n">
         <v>45723</v>
       </c>
-      <c r="P9" s="118" t="s">
-        <v>399</v>
+      <c r="P9" s="119" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4435,7 +4435,7 @@
       <c r="B10" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="119" t="n">
+      <c r="C10" s="120" t="n">
         <v>706082031</v>
       </c>
       <c r="D10" s="106" t="n">
@@ -4448,43 +4448,43 @@
       </c>
       <c r="H10" s="106"/>
       <c r="I10" s="106"/>
-      <c r="J10" s="117" t="n">
+      <c r="J10" s="118" t="n">
         <v>10750</v>
       </c>
       <c r="K10" s="107"/>
-      <c r="L10" s="109"/>
-      <c r="M10" s="109"/>
-      <c r="N10" s="109"/>
+      <c r="L10" s="110"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="110"/>
       <c r="O10" s="101" t="n">
         <v>45723</v>
       </c>
       <c r="P10" s="102" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="120" t="n">
+      <c r="A11" s="121" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="121" t="s">
+      <c r="B11" s="122" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="122"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="124" t="n">
-        <v>250</v>
-      </c>
-      <c r="H11" s="123"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="126"/>
-      <c r="K11" s="124"/>
-      <c r="L11" s="127"/>
-      <c r="M11" s="127"/>
-      <c r="N11" s="127"/>
-      <c r="O11" s="128"/>
-      <c r="P11" s="129"/>
+      <c r="C11" s="123"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="125" t="n">
+        <v>250</v>
+      </c>
+      <c r="H11" s="124"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="125"/>
+      <c r="L11" s="128"/>
+      <c r="M11" s="128"/>
+      <c r="N11" s="128"/>
+      <c r="O11" s="129"/>
+      <c r="P11" s="130"/>
     </row>
     <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="103" t="n">
@@ -4496,7 +4496,7 @@
       <c r="C12" s="105" t="n">
         <v>796721103</v>
       </c>
-      <c r="D12" s="130" t="n">
+      <c r="D12" s="131" t="n">
         <v>9500</v>
       </c>
       <c r="E12" s="103"/>
@@ -4506,18 +4506,18 @@
       </c>
       <c r="H12" s="103"/>
       <c r="I12" s="103"/>
-      <c r="J12" s="117" t="n">
+      <c r="J12" s="118" t="n">
         <v>9500</v>
       </c>
       <c r="K12" s="103"/>
-      <c r="L12" s="109"/>
-      <c r="M12" s="109"/>
-      <c r="N12" s="109"/>
+      <c r="L12" s="110"/>
+      <c r="M12" s="110"/>
+      <c r="N12" s="110"/>
       <c r="O12" s="101" t="n">
         <v>45968</v>
       </c>
       <c r="P12" s="102" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4527,7 +4527,7 @@
       <c r="B13" s="104" t="s">
         <v>136</v>
       </c>
-      <c r="C13" s="119" t="n">
+      <c r="C13" s="120" t="n">
         <v>792896940</v>
       </c>
       <c r="D13" s="106" t="n">
@@ -4540,28 +4540,28 @@
       </c>
       <c r="H13" s="106"/>
       <c r="I13" s="106"/>
-      <c r="J13" s="117" t="n">
+      <c r="J13" s="118" t="n">
         <v>9500</v>
       </c>
       <c r="K13" s="107"/>
-      <c r="L13" s="109"/>
-      <c r="M13" s="109"/>
-      <c r="N13" s="109"/>
+      <c r="L13" s="110"/>
+      <c r="M13" s="110"/>
+      <c r="N13" s="110"/>
       <c r="O13" s="101" t="s">
-        <v>402</v>
-      </c>
-      <c r="P13" s="118" t="s">
-        <v>403</v>
+        <v>404</v>
+      </c>
+      <c r="P13" s="119" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="103" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="131" t="s">
+      <c r="B14" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="119" t="n">
+      <c r="C14" s="120" t="n">
         <v>728513304</v>
       </c>
       <c r="D14" s="106" t="n">
@@ -4576,22 +4576,22 @@
       </c>
       <c r="H14" s="106"/>
       <c r="I14" s="106"/>
-      <c r="J14" s="117"/>
+      <c r="J14" s="118"/>
       <c r="K14" s="107"/>
-      <c r="L14" s="109"/>
-      <c r="M14" s="109"/>
-      <c r="N14" s="109"/>
+      <c r="L14" s="110"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="110"/>
       <c r="O14" s="101"/>
-      <c r="P14" s="118"/>
+      <c r="P14" s="119"/>
     </row>
     <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="88" t="n">
         <v>9</v>
       </c>
       <c r="B15" s="95" t="s">
-        <v>404</v>
-      </c>
-      <c r="C15" s="132" t="n">
+        <v>406</v>
+      </c>
+      <c r="C15" s="133" t="n">
         <v>710621587</v>
       </c>
       <c r="D15" s="97" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="H15" s="97"/>
       <c r="I15" s="97"/>
-      <c r="J15" s="117" t="n">
+      <c r="J15" s="118" t="n">
         <v>11250</v>
       </c>
       <c r="K15" s="98"/>
@@ -4614,8 +4614,8 @@
       <c r="O15" s="101" t="n">
         <v>45845</v>
       </c>
-      <c r="P15" s="133" t="s">
-        <v>405</v>
+      <c r="P15" s="134" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4625,7 +4625,7 @@
       <c r="B16" s="95" t="s">
         <v>298</v>
       </c>
-      <c r="C16" s="132" t="n">
+      <c r="C16" s="133" t="n">
         <v>768218105</v>
       </c>
       <c r="D16" s="97" t="n">
@@ -4640,18 +4640,18 @@
       </c>
       <c r="H16" s="97"/>
       <c r="I16" s="97"/>
-      <c r="J16" s="117" t="n">
+      <c r="J16" s="118" t="n">
         <v>10500</v>
       </c>
       <c r="K16" s="98"/>
-      <c r="L16" s="134"/>
+      <c r="L16" s="135"/>
       <c r="M16" s="92"/>
       <c r="N16" s="92"/>
       <c r="O16" s="101" t="n">
         <v>-648086</v>
       </c>
       <c r="P16" s="102" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4661,7 +4661,7 @@
       <c r="B17" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="119" t="n">
+      <c r="C17" s="120" t="n">
         <v>703706971</v>
       </c>
       <c r="D17" s="106" t="n">
@@ -4674,18 +4674,18 @@
       </c>
       <c r="H17" s="106"/>
       <c r="I17" s="106"/>
-      <c r="J17" s="117" t="n">
+      <c r="J17" s="118" t="n">
         <v>11250</v>
       </c>
       <c r="K17" s="107"/>
-      <c r="L17" s="109"/>
-      <c r="M17" s="109"/>
-      <c r="N17" s="109"/>
+      <c r="L17" s="110"/>
+      <c r="M17" s="110"/>
+      <c r="N17" s="110"/>
       <c r="O17" s="101" t="n">
         <v>45784</v>
       </c>
-      <c r="P17" s="118" t="s">
-        <v>407</v>
+      <c r="P17" s="119" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4695,7 +4695,7 @@
       <c r="B18" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="119" t="n">
+      <c r="C18" s="120" t="n">
         <v>727026360</v>
       </c>
       <c r="D18" s="106" t="n">
@@ -4708,18 +4708,18 @@
       </c>
       <c r="H18" s="106"/>
       <c r="I18" s="106"/>
-      <c r="J18" s="117" t="n">
+      <c r="J18" s="118" t="n">
         <v>11250</v>
       </c>
       <c r="K18" s="107"/>
-      <c r="L18" s="109"/>
-      <c r="M18" s="109"/>
-      <c r="N18" s="109"/>
+      <c r="L18" s="110"/>
+      <c r="M18" s="110"/>
+      <c r="N18" s="110"/>
       <c r="O18" s="101" t="n">
         <v>45876</v>
       </c>
-      <c r="P18" s="118" t="s">
-        <v>408</v>
+      <c r="P18" s="119" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4744,13 +4744,13 @@
       </c>
       <c r="H19" s="106"/>
       <c r="I19" s="106"/>
-      <c r="J19" s="117"/>
+      <c r="J19" s="118"/>
       <c r="K19" s="107"/>
-      <c r="L19" s="135"/>
-      <c r="M19" s="109"/>
-      <c r="N19" s="109"/>
-      <c r="O19" s="136"/>
-      <c r="P19" s="137"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="137"/>
+      <c r="P19" s="138"/>
     </row>
     <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="103" t="n">
@@ -4762,7 +4762,7 @@
       <c r="C20" s="105" t="n">
         <v>111236304</v>
       </c>
-      <c r="D20" s="130" t="n">
+      <c r="D20" s="131" t="n">
         <v>11000</v>
       </c>
       <c r="E20" s="103"/>
@@ -4770,56 +4770,56 @@
       <c r="G20" s="107" t="n">
         <v>250</v>
       </c>
-      <c r="H20" s="138"/>
-      <c r="I20" s="138"/>
-      <c r="J20" s="117" t="n">
+      <c r="H20" s="139"/>
+      <c r="I20" s="139"/>
+      <c r="J20" s="118" t="n">
         <v>11250</v>
       </c>
       <c r="K20" s="103"/>
-      <c r="L20" s="109"/>
-      <c r="M20" s="109"/>
-      <c r="N20" s="109"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
       <c r="O20" s="101" t="n">
         <v>45784</v>
       </c>
-      <c r="P20" s="139" t="s">
-        <v>409</v>
+      <c r="P20" s="140" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="111" t="n">
+      <c r="A21" s="112" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="112" t="s">
+      <c r="B21" s="113" t="s">
         <v>51</v>
       </c>
       <c r="C21" s="105" t="n">
         <v>723022756</v>
       </c>
-      <c r="D21" s="114" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E21" s="115"/>
-      <c r="F21" s="116" t="n">
+      <c r="D21" s="115" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E21" s="116"/>
+      <c r="F21" s="117" t="n">
         <v>20150</v>
       </c>
       <c r="G21" s="107" t="n">
         <v>250</v>
       </c>
-      <c r="H21" s="114"/>
-      <c r="I21" s="114"/>
-      <c r="J21" s="117" t="n">
+      <c r="H21" s="115"/>
+      <c r="I21" s="115"/>
+      <c r="J21" s="118" t="n">
         <v>17300</v>
       </c>
-      <c r="K21" s="115"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="110"/>
+      <c r="M21" s="110"/>
+      <c r="N21" s="110"/>
       <c r="O21" s="101" t="n">
         <v>45695</v>
       </c>
-      <c r="P21" s="137" t="s">
-        <v>410</v>
+      <c r="P21" s="138" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4829,7 +4829,7 @@
       <c r="B22" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="119" t="n">
+      <c r="C22" s="120" t="n">
         <v>705321457</v>
       </c>
       <c r="D22" s="106" t="n">
@@ -4844,11 +4844,11 @@
       </c>
       <c r="H22" s="106"/>
       <c r="I22" s="106"/>
-      <c r="J22" s="117"/>
+      <c r="J22" s="118"/>
       <c r="K22" s="107"/>
-      <c r="L22" s="109"/>
-      <c r="M22" s="109"/>
-      <c r="N22" s="109"/>
+      <c r="L22" s="110"/>
+      <c r="M22" s="110"/>
+      <c r="N22" s="110"/>
       <c r="O22" s="101"/>
       <c r="P22" s="102"/>
     </row>
@@ -4859,7 +4859,7 @@
       <c r="B23" s="95" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="132" t="n">
+      <c r="C23" s="133" t="n">
         <v>726518863</v>
       </c>
       <c r="D23" s="97" t="n">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="H23" s="97"/>
       <c r="I23" s="97"/>
-      <c r="J23" s="117" t="n">
+      <c r="J23" s="118" t="n">
         <v>11250</v>
       </c>
       <c r="K23" s="98"/>
@@ -4882,8 +4882,8 @@
       <c r="O23" s="101" t="n">
         <v>45845</v>
       </c>
-      <c r="P23" s="110" t="s">
-        <v>411</v>
+      <c r="P23" s="111" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4893,7 +4893,7 @@
       <c r="B24" s="95" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="132" t="n">
+      <c r="C24" s="133" t="n">
         <v>727516082</v>
       </c>
       <c r="D24" s="97" t="n">
@@ -4906,18 +4906,18 @@
       </c>
       <c r="H24" s="97"/>
       <c r="I24" s="97"/>
-      <c r="J24" s="117" t="n">
+      <c r="J24" s="118" t="n">
         <v>11250</v>
       </c>
       <c r="K24" s="98"/>
-      <c r="L24" s="134"/>
+      <c r="L24" s="135"/>
       <c r="M24" s="92"/>
       <c r="N24" s="92"/>
       <c r="O24" s="101" t="n">
         <v>45754</v>
       </c>
       <c r="P24" s="102" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4927,7 +4927,7 @@
       <c r="B25" s="104" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="119" t="n">
+      <c r="C25" s="120" t="n">
         <v>706651018</v>
       </c>
       <c r="D25" s="106" t="n">
@@ -4942,13 +4942,13 @@
       </c>
       <c r="H25" s="106"/>
       <c r="I25" s="106"/>
-      <c r="J25" s="117"/>
+      <c r="J25" s="118"/>
       <c r="K25" s="107"/>
-      <c r="L25" s="109"/>
-      <c r="M25" s="109"/>
-      <c r="N25" s="109"/>
-      <c r="O25" s="140"/>
-      <c r="P25" s="118"/>
+      <c r="L25" s="110"/>
+      <c r="M25" s="110"/>
+      <c r="N25" s="110"/>
+      <c r="O25" s="141"/>
+      <c r="P25" s="119"/>
     </row>
     <row r="26" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="88" t="n">
@@ -4957,7 +4957,7 @@
       <c r="B26" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="132" t="n">
+      <c r="C26" s="133" t="n">
         <v>718723801</v>
       </c>
       <c r="D26" s="97" t="n">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="H26" s="97"/>
       <c r="I26" s="97"/>
-      <c r="J26" s="117" t="n">
+      <c r="J26" s="118" t="n">
         <v>11250</v>
       </c>
       <c r="K26" s="98"/>
@@ -4980,8 +4980,8 @@
       <c r="O26" s="101" t="n">
         <v>45723</v>
       </c>
-      <c r="P26" s="141" t="s">
-        <v>413</v>
+      <c r="P26" s="142" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5004,20 +5004,20 @@
       <c r="G27" s="98" t="n">
         <v>250</v>
       </c>
-      <c r="H27" s="142"/>
+      <c r="H27" s="143"/>
       <c r="I27" s="106"/>
-      <c r="J27" s="117" t="n">
+      <c r="J27" s="118" t="n">
         <v>10500</v>
       </c>
       <c r="K27" s="107"/>
-      <c r="L27" s="109"/>
-      <c r="M27" s="109"/>
-      <c r="N27" s="109"/>
+      <c r="L27" s="110"/>
+      <c r="M27" s="110"/>
+      <c r="N27" s="110"/>
       <c r="O27" s="101" t="n">
         <v>45695</v>
       </c>
       <c r="P27" s="102" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5025,7 +5025,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="104" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C28" s="105" t="n">
         <v>101921686</v>
@@ -5040,18 +5040,18 @@
       </c>
       <c r="H28" s="106"/>
       <c r="I28" s="106"/>
-      <c r="J28" s="117" t="n">
+      <c r="J28" s="118" t="n">
         <v>11250</v>
       </c>
       <c r="K28" s="107"/>
-      <c r="L28" s="109"/>
-      <c r="M28" s="109"/>
-      <c r="N28" s="109"/>
-      <c r="O28" s="143" t="n">
+      <c r="L28" s="110"/>
+      <c r="M28" s="110"/>
+      <c r="N28" s="110"/>
+      <c r="O28" s="144" t="n">
         <v>45968</v>
       </c>
       <c r="P28" s="102" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H29" s="106"/>
       <c r="I29" s="106"/>
-      <c r="J29" s="117" t="n">
+      <c r="J29" s="118" t="n">
         <v>11000</v>
       </c>
       <c r="K29" s="107"/>
@@ -5086,72 +5086,72 @@
       <c r="O29" s="101" t="n">
         <v>45784</v>
       </c>
-      <c r="P29" s="144" t="s">
-        <v>417</v>
+      <c r="P29" s="145" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="145" t="n">
+      <c r="A30" s="146" t="n">
         <v>24</v>
       </c>
       <c r="B30" s="95" t="s">
-        <v>418</v>
-      </c>
-      <c r="C30" s="119" t="n">
+        <v>420</v>
+      </c>
+      <c r="C30" s="120" t="n">
         <v>717334827</v>
       </c>
-      <c r="D30" s="146" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E30" s="147"/>
-      <c r="F30" s="148" t="n">
+      <c r="D30" s="147" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E30" s="148"/>
+      <c r="F30" s="149" t="n">
         <v>6250</v>
       </c>
       <c r="G30" s="98" t="n">
         <v>250</v>
       </c>
-      <c r="H30" s="146"/>
-      <c r="I30" s="146"/>
-      <c r="J30" s="117" t="n">
-        <v>11250</v>
-      </c>
-      <c r="K30" s="147"/>
+      <c r="H30" s="147"/>
+      <c r="I30" s="147"/>
+      <c r="J30" s="118" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K30" s="148"/>
       <c r="L30" s="92"/>
       <c r="M30" s="92"/>
       <c r="N30" s="92"/>
       <c r="O30" s="101" t="n">
         <v>45845</v>
       </c>
-      <c r="P30" s="149" t="s">
-        <v>419</v>
+      <c r="P30" s="150" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="150" t="n">
+      <c r="A31" s="151" t="n">
         <v>25</v>
       </c>
-      <c r="B31" s="151" t="s">
+      <c r="B31" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="152" t="n">
+      <c r="C31" s="153" t="n">
         <v>712298540</v>
       </c>
-      <c r="D31" s="153" t="n">
+      <c r="D31" s="154" t="n">
         <v>12000</v>
       </c>
-      <c r="E31" s="153"/>
-      <c r="F31" s="154" t="n">
+      <c r="E31" s="154"/>
+      <c r="F31" s="155" t="n">
         <v>17750</v>
       </c>
       <c r="G31" s="98" t="n">
         <v>250</v>
       </c>
-      <c r="H31" s="153"/>
-      <c r="I31" s="153"/>
-      <c r="J31" s="117" t="n">
+      <c r="H31" s="154"/>
+      <c r="I31" s="154"/>
+      <c r="J31" s="118" t="n">
         <v>15000</v>
       </c>
-      <c r="K31" s="153"/>
+      <c r="K31" s="154"/>
       <c r="L31" s="92"/>
       <c r="M31" s="92"/>
       <c r="N31" s="92"/>
@@ -5159,33 +5159,33 @@
         <v>45998</v>
       </c>
       <c r="P31" s="102" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="150" t="n">
+      <c r="A32" s="151" t="n">
         <v>26</v>
       </c>
       <c r="B32" s="95" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="152" t="n">
+      <c r="C32" s="153" t="n">
         <v>114717120</v>
       </c>
-      <c r="D32" s="153" t="n">
+      <c r="D32" s="154" t="n">
         <v>12000</v>
       </c>
-      <c r="E32" s="153" t="n">
+      <c r="E32" s="154" t="n">
         <v>12000</v>
       </c>
-      <c r="F32" s="154"/>
+      <c r="F32" s="155"/>
       <c r="G32" s="98" t="n">
         <v>250</v>
       </c>
-      <c r="H32" s="153"/>
-      <c r="I32" s="153"/>
-      <c r="J32" s="117"/>
-      <c r="K32" s="153"/>
+      <c r="H32" s="154"/>
+      <c r="I32" s="154"/>
+      <c r="J32" s="118"/>
+      <c r="K32" s="154"/>
       <c r="L32" s="92"/>
       <c r="M32" s="92"/>
       <c r="N32" s="92"/>
@@ -5193,161 +5193,167 @@
       <c r="P32" s="102"/>
     </row>
     <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="150" t="n">
+      <c r="A33" s="151" t="n">
         <v>27</v>
       </c>
-      <c r="B33" s="155" t="s">
-        <v>421</v>
-      </c>
-      <c r="C33" s="156" t="s">
-        <v>422</v>
-      </c>
-      <c r="D33" s="153" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E33" s="153"/>
-      <c r="F33" s="154"/>
+      <c r="B33" s="156" t="s">
+        <v>423</v>
+      </c>
+      <c r="C33" s="157" t="s">
+        <v>424</v>
+      </c>
+      <c r="D33" s="154" t="n">
+        <v>12250</v>
+      </c>
+      <c r="E33" s="154"/>
+      <c r="F33" s="155"/>
       <c r="G33" s="98" t="n">
         <v>250</v>
       </c>
-      <c r="H33" s="153"/>
-      <c r="I33" s="153"/>
-      <c r="J33" s="117"/>
-      <c r="K33" s="153"/>
+      <c r="H33" s="154"/>
+      <c r="I33" s="154"/>
+      <c r="J33" s="118" t="n">
+        <v>12250</v>
+      </c>
+      <c r="K33" s="154"/>
       <c r="L33" s="92"/>
       <c r="M33" s="92"/>
       <c r="N33" s="92"/>
-      <c r="O33" s="101"/>
-      <c r="P33" s="144"/>
+      <c r="O33" s="101" t="s">
+        <v>425</v>
+      </c>
+      <c r="P33" s="145" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="150" t="n">
+      <c r="A34" s="151" t="n">
         <v>28</v>
       </c>
-      <c r="B34" s="151" t="s">
+      <c r="B34" s="152" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="152" t="n">
+      <c r="C34" s="153" t="n">
         <v>713597010</v>
       </c>
-      <c r="D34" s="153" t="n">
+      <c r="D34" s="154" t="n">
         <v>12000</v>
       </c>
-      <c r="E34" s="153"/>
-      <c r="F34" s="154" t="n">
+      <c r="E34" s="154"/>
+      <c r="F34" s="155" t="n">
         <v>19500</v>
       </c>
       <c r="G34" s="98" t="n">
         <v>250</v>
       </c>
-      <c r="H34" s="153"/>
-      <c r="I34" s="153"/>
-      <c r="J34" s="117" t="n">
+      <c r="H34" s="154"/>
+      <c r="I34" s="154"/>
+      <c r="J34" s="118" t="n">
         <v>15000</v>
       </c>
-      <c r="K34" s="153"/>
-      <c r="L34" s="157"/>
-      <c r="N34" s="158"/>
+      <c r="K34" s="154"/>
+      <c r="L34" s="158"/>
+      <c r="N34" s="159"/>
       <c r="O34" s="101" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="P34" s="102" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="150" t="n">
+      <c r="A35" s="151" t="n">
         <v>29</v>
       </c>
-      <c r="B35" s="151" t="s">
+      <c r="B35" s="152" t="s">
         <v>388</v>
       </c>
-      <c r="C35" s="152" t="n">
+      <c r="C35" s="153" t="n">
         <v>726516413</v>
       </c>
-      <c r="D35" s="153" t="n">
+      <c r="D35" s="154" t="n">
         <v>12000</v>
       </c>
-      <c r="E35" s="153"/>
-      <c r="F35" s="154"/>
+      <c r="E35" s="154"/>
+      <c r="F35" s="155"/>
       <c r="G35" s="98" t="n">
         <v>250</v>
       </c>
-      <c r="H35" s="153"/>
-      <c r="I35" s="153"/>
-      <c r="J35" s="117" t="n">
+      <c r="H35" s="154"/>
+      <c r="I35" s="154"/>
+      <c r="J35" s="118" t="n">
         <v>12500</v>
       </c>
-      <c r="K35" s="153"/>
+      <c r="K35" s="154"/>
       <c r="L35" s="92"/>
       <c r="M35" s="92"/>
       <c r="N35" s="92"/>
-      <c r="O35" s="143" t="s">
-        <v>425</v>
-      </c>
-      <c r="P35" s="159" t="s">
-        <v>426</v>
+      <c r="O35" s="144" t="s">
+        <v>429</v>
+      </c>
+      <c r="P35" s="160" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="150" t="n">
+      <c r="A36" s="151" t="n">
         <v>30</v>
       </c>
-      <c r="B36" s="151" t="s">
+      <c r="B36" s="152" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="156" t="n">
+      <c r="C36" s="157" t="n">
         <v>713171316</v>
       </c>
-      <c r="D36" s="153" t="n">
+      <c r="D36" s="154" t="n">
         <v>12000</v>
       </c>
-      <c r="E36" s="153"/>
-      <c r="F36" s="154" t="n">
+      <c r="E36" s="154"/>
+      <c r="F36" s="155" t="n">
         <v>12000</v>
       </c>
       <c r="G36" s="98" t="n">
         <v>250</v>
       </c>
-      <c r="H36" s="153"/>
-      <c r="I36" s="153"/>
-      <c r="J36" s="160" t="n">
+      <c r="H36" s="154"/>
+      <c r="I36" s="154"/>
+      <c r="J36" s="161" t="n">
         <v>12250</v>
       </c>
-      <c r="K36" s="153"/>
+      <c r="K36" s="154"/>
       <c r="L36" s="92"/>
       <c r="M36" s="92"/>
       <c r="N36" s="92"/>
-      <c r="O36" s="136" t="s">
-        <v>427</v>
+      <c r="O36" s="137" t="s">
+        <v>431</v>
       </c>
       <c r="P36" s="102" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="161" t="n">
+      <c r="A37" s="109" t="n">
         <v>31</v>
       </c>
       <c r="B37" s="95" t="s">
-        <v>429</v>
-      </c>
-      <c r="C37" s="132" t="s">
-        <v>430</v>
-      </c>
-      <c r="D37" s="161" t="n">
+        <v>433</v>
+      </c>
+      <c r="C37" s="133" t="s">
+        <v>423</v>
+      </c>
+      <c r="D37" s="109" t="n">
         <v>12000</v>
       </c>
-      <c r="E37" s="161"/>
+      <c r="E37" s="109"/>
       <c r="F37" s="162" t="n">
         <v>12250</v>
       </c>
       <c r="G37" s="98" t="n">
         <v>250</v>
       </c>
-      <c r="H37" s="161"/>
-      <c r="I37" s="161"/>
-      <c r="J37" s="117" t="n">
+      <c r="H37" s="109"/>
+      <c r="I37" s="109"/>
+      <c r="J37" s="118" t="n">
         <v>12250</v>
       </c>
       <c r="K37" s="88"/>
@@ -5358,30 +5364,30 @@
         <v>45876</v>
       </c>
       <c r="P37" s="102" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="161" t="n">
+      <c r="A38" s="109" t="n">
         <v>32</v>
       </c>
       <c r="B38" s="95" t="s">
-        <v>429</v>
-      </c>
-      <c r="C38" s="132" t="n">
+        <v>433</v>
+      </c>
+      <c r="C38" s="133" t="n">
         <v>707653219</v>
       </c>
-      <c r="D38" s="163" t="n">
+      <c r="D38" s="100" t="n">
         <v>11750</v>
       </c>
       <c r="E38" s="88"/>
-      <c r="F38" s="164"/>
+      <c r="F38" s="163"/>
       <c r="G38" s="98" t="n">
         <v>250</v>
       </c>
-      <c r="H38" s="161"/>
-      <c r="I38" s="161"/>
-      <c r="J38" s="160" t="n">
+      <c r="H38" s="109"/>
+      <c r="I38" s="109"/>
+      <c r="J38" s="161" t="n">
         <v>11250</v>
       </c>
       <c r="K38" s="88"/>
@@ -5392,100 +5398,100 @@
         <v>45695</v>
       </c>
       <c r="P38" s="102" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="88"/>
-      <c r="B39" s="161"/>
-      <c r="C39" s="163"/>
-      <c r="D39" s="165" t="n">
+      <c r="B39" s="109"/>
+      <c r="C39" s="100"/>
+      <c r="D39" s="164" t="n">
         <f aca="false">SUM(D7:D38)</f>
-        <v>340750</v>
-      </c>
-      <c r="E39" s="166" t="n">
+        <v>341000</v>
+      </c>
+      <c r="E39" s="165" t="n">
         <v>12000</v>
       </c>
-      <c r="F39" s="166"/>
-      <c r="G39" s="166" t="n">
+      <c r="F39" s="165"/>
+      <c r="G39" s="165" t="n">
         <v>8000</v>
       </c>
-      <c r="H39" s="166"/>
-      <c r="I39" s="166"/>
-      <c r="J39" s="167" t="n">
+      <c r="H39" s="165"/>
+      <c r="I39" s="165"/>
+      <c r="J39" s="100" t="n">
         <f aca="false">SUM(J7:J38)</f>
-        <v>278800</v>
-      </c>
-      <c r="K39" s="166"/>
-      <c r="L39" s="166"/>
-      <c r="M39" s="166"/>
-      <c r="N39" s="166"/>
-      <c r="O39" s="168"/>
+        <v>301300</v>
+      </c>
+      <c r="K39" s="165"/>
+      <c r="L39" s="165"/>
+      <c r="M39" s="165"/>
+      <c r="N39" s="165"/>
+      <c r="O39" s="166"/>
       <c r="P39" s="88"/>
     </row>
     <row r="40" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="169" t="s">
+      <c r="B40" s="167" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="169" t="n">
+      <c r="C40" s="167" t="n">
         <f aca="false">SUM(J8:J38)</f>
-        <v>268800</v>
-      </c>
-      <c r="E40" s="170"/>
+        <v>291300</v>
+      </c>
+      <c r="E40" s="168"/>
     </row>
     <row r="41" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="161" t="s">
+      <c r="B41" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="161"/>
-      <c r="D41" s="171"/>
-      <c r="F41" s="172"/>
-      <c r="G41" s="172"/>
-      <c r="H41" s="172"/>
+      <c r="C41" s="109"/>
+      <c r="D41" s="169"/>
+      <c r="F41" s="170"/>
+      <c r="G41" s="170"/>
+      <c r="H41" s="170"/>
     </row>
     <row r="42" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="161"/>
-      <c r="C42" s="163"/>
-      <c r="F42" s="172"/>
-      <c r="G42" s="172"/>
-      <c r="H42" s="172"/>
+      <c r="B42" s="109"/>
+      <c r="C42" s="100"/>
+      <c r="F42" s="170"/>
+      <c r="G42" s="170"/>
+      <c r="H42" s="170"/>
     </row>
     <row r="43" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="171" t="s">
+      <c r="B43" s="169" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="173"/>
-      <c r="F43" s="172"/>
-      <c r="G43" s="172"/>
-      <c r="H43" s="172"/>
+      <c r="C43" s="171"/>
+      <c r="F43" s="170"/>
+      <c r="G43" s="170"/>
+      <c r="H43" s="170"/>
     </row>
     <row r="44" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="161"/>
-      <c r="C44" s="161"/>
+      <c r="B44" s="109"/>
+      <c r="C44" s="109"/>
     </row>
     <row r="45" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="161" t="s">
-        <v>433</v>
-      </c>
-      <c r="C45" s="161"/>
+      <c r="B45" s="109" t="s">
+        <v>436</v>
+      </c>
+      <c r="C45" s="109"/>
     </row>
     <row r="46" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="161" t="s">
+      <c r="B46" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="161"/>
+      <c r="C46" s="109"/>
     </row>
     <row r="47" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="161" t="s">
+      <c r="B47" s="109" t="s">
         <v>89</v>
       </c>
-      <c r="C47" s="161"/>
+      <c r="C47" s="109"/>
     </row>
     <row r="48" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="161" t="s">
+      <c r="B48" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="C48" s="161"/>
+      <c r="C48" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/PROPERTIES/QYOTA/QYOTA 2025.xlsx
+++ b/PROPERTIES/QYOTA/QYOTA 2025.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="439">
   <si>
     <t xml:space="preserve">COURTLAND REALTORS LTD P.O.BOX 11993, NAIROBI</t>
   </si>
@@ -1247,6 +1247,12 @@
   </si>
   <si>
     <t xml:space="preserve">TFJ6IUAC8I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGS4TZZMRQ</t>
   </si>
   <si>
     <t xml:space="preserve">PRISCILLA NDIRANGU</t>
@@ -4576,20 +4582,26 @@
       </c>
       <c r="H14" s="106"/>
       <c r="I14" s="106"/>
-      <c r="J14" s="118"/>
+      <c r="J14" s="118" t="n">
+        <v>10500</v>
+      </c>
       <c r="K14" s="107"/>
       <c r="L14" s="110"/>
       <c r="M14" s="110"/>
       <c r="N14" s="110"/>
-      <c r="O14" s="101"/>
-      <c r="P14" s="119"/>
+      <c r="O14" s="101" t="s">
+        <v>406</v>
+      </c>
+      <c r="P14" s="119" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="88" t="n">
         <v>9</v>
       </c>
       <c r="B15" s="95" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C15" s="133" t="n">
         <v>710621587</v>
@@ -4615,7 +4627,7 @@
         <v>45845</v>
       </c>
       <c r="P15" s="134" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4651,7 +4663,7 @@
         <v>-648086</v>
       </c>
       <c r="P16" s="102" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4685,7 +4697,7 @@
         <v>45784</v>
       </c>
       <c r="P17" s="119" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4719,7 +4731,7 @@
         <v>45876</v>
       </c>
       <c r="P18" s="119" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4783,7 +4795,7 @@
         <v>45784</v>
       </c>
       <c r="P20" s="140" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4819,7 +4831,7 @@
         <v>45695</v>
       </c>
       <c r="P21" s="138" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4883,7 +4895,7 @@
         <v>45845</v>
       </c>
       <c r="P23" s="111" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4917,7 +4929,7 @@
         <v>45754</v>
       </c>
       <c r="P24" s="102" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4981,7 +4993,7 @@
         <v>45723</v>
       </c>
       <c r="P26" s="142" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5017,7 +5029,7 @@
         <v>45695</v>
       </c>
       <c r="P27" s="102" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5025,7 +5037,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="104" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C28" s="105" t="n">
         <v>101921686</v>
@@ -5051,7 +5063,7 @@
         <v>45968</v>
       </c>
       <c r="P28" s="102" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5087,7 +5099,7 @@
         <v>45784</v>
       </c>
       <c r="P29" s="145" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5095,7 +5107,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="95" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C30" s="120" t="n">
         <v>717334827</v>
@@ -5123,7 +5135,7 @@
         <v>45845</v>
       </c>
       <c r="P30" s="150" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5159,7 +5171,7 @@
         <v>45998</v>
       </c>
       <c r="P31" s="102" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5197,10 +5209,10 @@
         <v>27</v>
       </c>
       <c r="B33" s="156" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C33" s="157" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D33" s="154" t="n">
         <v>12250</v>
@@ -5220,10 +5232,10 @@
       <c r="M33" s="92"/>
       <c r="N33" s="92"/>
       <c r="O33" s="101" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P33" s="145" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5255,10 +5267,10 @@
       <c r="L34" s="158"/>
       <c r="N34" s="159"/>
       <c r="O34" s="101" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="P34" s="102" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5289,10 +5301,10 @@
       <c r="M35" s="92"/>
       <c r="N35" s="92"/>
       <c r="O35" s="144" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P35" s="160" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5325,10 +5337,10 @@
       <c r="M36" s="92"/>
       <c r="N36" s="92"/>
       <c r="O36" s="137" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="P36" s="102" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5336,10 +5348,10 @@
         <v>31</v>
       </c>
       <c r="B37" s="95" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C37" s="133" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D37" s="109" t="n">
         <v>12000</v>
@@ -5364,7 +5376,7 @@
         <v>45876</v>
       </c>
       <c r="P37" s="102" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5372,7 +5384,7 @@
         <v>32</v>
       </c>
       <c r="B38" s="95" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C38" s="133" t="n">
         <v>707653219</v>
@@ -5398,7 +5410,7 @@
         <v>45695</v>
       </c>
       <c r="P38" s="102" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5420,7 +5432,7 @@
       <c r="I39" s="165"/>
       <c r="J39" s="100" t="n">
         <f aca="false">SUM(J7:J38)</f>
-        <v>301300</v>
+        <v>311800</v>
       </c>
       <c r="K39" s="165"/>
       <c r="L39" s="165"/>
@@ -5435,7 +5447,7 @@
       </c>
       <c r="C40" s="167" t="n">
         <f aca="false">SUM(J8:J38)</f>
-        <v>291300</v>
+        <v>301800</v>
       </c>
       <c r="E40" s="168"/>
     </row>
@@ -5471,7 +5483,7 @@
     </row>
     <row r="45" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="109" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C45" s="109"/>
     </row>

--- a/PROPERTIES/QYOTA/QYOTA 2025.xlsx
+++ b/PROPERTIES/QYOTA/QYOTA 2025.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="OCT" sheetId="1" state="visible" r:id="rId3"/>
@@ -18,6 +18,7 @@
     <sheet name="MAY" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="JUNE" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="JULY" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="AUG" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="439">
   <si>
     <t xml:space="preserve">COURTLAND REALTORS LTD P.O.BOX 11993, NAIROBI</t>
   </si>
@@ -5524,6 +5525,1192 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:P48"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="87" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="87" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="87" width="27.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="87" width="20.97"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="5" style="87" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="87" width="19.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="87" width="17.23"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="10" style="87" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="87" width="21.32"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="13" style="87" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="87" width="18.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="87" width="22.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="87" width="21.56"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="3"/>
+      <c r="P2" s="87" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="3"/>
+      <c r="P3" s="87" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="88"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+    </row>
+    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="89"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="91" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="91"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="92"/>
+      <c r="M5" s="92"/>
+      <c r="N5" s="92"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="92"/>
+    </row>
+    <row r="6" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="91" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="91" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="91" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="91" t="s">
+        <v>395</v>
+      </c>
+      <c r="I6" s="91" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" s="90" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="90" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="90" t="s">
+        <v>396</v>
+      </c>
+      <c r="O6" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="P6" s="89" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="95" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="96" t="n">
+        <v>703485579</v>
+      </c>
+      <c r="D7" s="97" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E7" s="98"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="98"/>
+      <c r="L7" s="88"/>
+      <c r="M7" s="88"/>
+      <c r="N7" s="88"/>
+      <c r="O7" s="101"/>
+      <c r="P7" s="102"/>
+    </row>
+    <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="103" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="104" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="105" t="n">
+        <v>726646115</v>
+      </c>
+      <c r="D8" s="106" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E8" s="107"/>
+      <c r="F8" s="108" t="n">
+        <v>10750</v>
+      </c>
+      <c r="G8" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H8" s="106"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="109"/>
+      <c r="K8" s="107"/>
+      <c r="L8" s="110"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="110"/>
+      <c r="O8" s="101"/>
+      <c r="P8" s="111"/>
+    </row>
+    <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="112" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="114" t="n">
+        <v>725840501</v>
+      </c>
+      <c r="D9" s="115" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E9" s="116"/>
+      <c r="F9" s="117" t="n">
+        <v>250</v>
+      </c>
+      <c r="G9" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H9" s="115"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="116"/>
+      <c r="L9" s="110"/>
+      <c r="M9" s="110"/>
+      <c r="N9" s="110"/>
+      <c r="O9" s="101"/>
+      <c r="P9" s="119"/>
+    </row>
+    <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="103" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="104" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="120" t="n">
+        <v>706082031</v>
+      </c>
+      <c r="D10" s="106" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E10" s="107"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H10" s="106"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="118"/>
+      <c r="K10" s="107"/>
+      <c r="L10" s="110"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="101"/>
+      <c r="P10" s="102"/>
+    </row>
+    <row r="11" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="121" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="122" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="123"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="125" t="n">
+        <v>250</v>
+      </c>
+      <c r="H11" s="124"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="125"/>
+      <c r="L11" s="128"/>
+      <c r="M11" s="128"/>
+      <c r="N11" s="128"/>
+      <c r="O11" s="129"/>
+      <c r="P11" s="130"/>
+    </row>
+    <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="103" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="104" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" s="105" t="n">
+        <v>796721103</v>
+      </c>
+      <c r="D12" s="131" t="n">
+        <v>9500</v>
+      </c>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H12" s="103"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="118"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="110"/>
+      <c r="M12" s="110"/>
+      <c r="N12" s="110"/>
+      <c r="O12" s="101"/>
+      <c r="P12" s="102"/>
+    </row>
+    <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="103" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="104" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="120" t="n">
+        <v>792896940</v>
+      </c>
+      <c r="D13" s="106" t="n">
+        <v>9500</v>
+      </c>
+      <c r="E13" s="107"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H13" s="106"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="118"/>
+      <c r="K13" s="107"/>
+      <c r="L13" s="110"/>
+      <c r="M13" s="110"/>
+      <c r="N13" s="110"/>
+      <c r="O13" s="101"/>
+      <c r="P13" s="119"/>
+    </row>
+    <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="103" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="132" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="120" t="n">
+        <v>728513304</v>
+      </c>
+      <c r="D14" s="106" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E14" s="107"/>
+      <c r="F14" s="108" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G14" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H14" s="106"/>
+      <c r="I14" s="106"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="107"/>
+      <c r="L14" s="110"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="110"/>
+      <c r="O14" s="101"/>
+      <c r="P14" s="119"/>
+    </row>
+    <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="88" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="95" t="s">
+        <v>408</v>
+      </c>
+      <c r="C15" s="133" t="n">
+        <v>710621587</v>
+      </c>
+      <c r="D15" s="97" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E15" s="98"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H15" s="97"/>
+      <c r="I15" s="97"/>
+      <c r="J15" s="118"/>
+      <c r="K15" s="98"/>
+      <c r="L15" s="92"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="92"/>
+      <c r="O15" s="101"/>
+      <c r="P15" s="134"/>
+    </row>
+    <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="88" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="95" t="s">
+        <v>298</v>
+      </c>
+      <c r="C16" s="133" t="n">
+        <v>768218105</v>
+      </c>
+      <c r="D16" s="97" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E16" s="98"/>
+      <c r="F16" s="99" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G16" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H16" s="97"/>
+      <c r="I16" s="97"/>
+      <c r="J16" s="118"/>
+      <c r="K16" s="98"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="92"/>
+      <c r="N16" s="92"/>
+      <c r="O16" s="101"/>
+      <c r="P16" s="102"/>
+    </row>
+    <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="103" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="104" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="120" t="n">
+        <v>703706971</v>
+      </c>
+      <c r="D17" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E17" s="107"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H17" s="106"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="118"/>
+      <c r="K17" s="107"/>
+      <c r="L17" s="110"/>
+      <c r="M17" s="110"/>
+      <c r="N17" s="110"/>
+      <c r="O17" s="101"/>
+      <c r="P17" s="119"/>
+    </row>
+    <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="103" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="104" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="120" t="n">
+        <v>727026360</v>
+      </c>
+      <c r="D18" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E18" s="107"/>
+      <c r="F18" s="108"/>
+      <c r="G18" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H18" s="106"/>
+      <c r="I18" s="106"/>
+      <c r="J18" s="118"/>
+      <c r="K18" s="107"/>
+      <c r="L18" s="110"/>
+      <c r="M18" s="110"/>
+      <c r="N18" s="110"/>
+      <c r="O18" s="101"/>
+      <c r="P18" s="119"/>
+    </row>
+    <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="103" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="104" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="105" t="n">
+        <v>739314188</v>
+      </c>
+      <c r="D19" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E19" s="107"/>
+      <c r="F19" s="108" t="n">
+        <v>41500</v>
+      </c>
+      <c r="G19" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H19" s="106"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="118"/>
+      <c r="K19" s="107"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="137"/>
+      <c r="P19" s="138"/>
+    </row>
+    <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="103" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="104" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="105" t="n">
+        <v>111236304</v>
+      </c>
+      <c r="D20" s="131" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E20" s="103"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H20" s="139"/>
+      <c r="I20" s="139"/>
+      <c r="J20" s="118"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="101"/>
+      <c r="P20" s="140"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="112" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="105" t="n">
+        <v>723022756</v>
+      </c>
+      <c r="D21" s="115" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E21" s="116"/>
+      <c r="F21" s="117" t="n">
+        <v>20150</v>
+      </c>
+      <c r="G21" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H21" s="115"/>
+      <c r="I21" s="115"/>
+      <c r="J21" s="118"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="110"/>
+      <c r="M21" s="110"/>
+      <c r="N21" s="110"/>
+      <c r="O21" s="101"/>
+      <c r="P21" s="138"/>
+    </row>
+    <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="103" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="120" t="n">
+        <v>705321457</v>
+      </c>
+      <c r="D22" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E22" s="107"/>
+      <c r="F22" s="108" t="n">
+        <v>11250</v>
+      </c>
+      <c r="G22" s="107" t="n">
+        <v>250</v>
+      </c>
+      <c r="H22" s="106"/>
+      <c r="I22" s="106"/>
+      <c r="J22" s="118"/>
+      <c r="K22" s="107"/>
+      <c r="L22" s="110"/>
+      <c r="M22" s="110"/>
+      <c r="N22" s="110"/>
+      <c r="O22" s="101"/>
+      <c r="P22" s="102"/>
+    </row>
+    <row r="23" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="88" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="95" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="133" t="n">
+        <v>726518863</v>
+      </c>
+      <c r="D23" s="97" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E23" s="98"/>
+      <c r="F23" s="99"/>
+      <c r="G23" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H23" s="97"/>
+      <c r="I23" s="97"/>
+      <c r="J23" s="118"/>
+      <c r="K23" s="98"/>
+      <c r="L23" s="92"/>
+      <c r="M23" s="92"/>
+      <c r="N23" s="92"/>
+      <c r="O23" s="101"/>
+      <c r="P23" s="111"/>
+    </row>
+    <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="88" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" s="95" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="133" t="n">
+        <v>727516082</v>
+      </c>
+      <c r="D24" s="97" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E24" s="98"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H24" s="97"/>
+      <c r="I24" s="97"/>
+      <c r="J24" s="118"/>
+      <c r="K24" s="98"/>
+      <c r="L24" s="135"/>
+      <c r="M24" s="92"/>
+      <c r="N24" s="92"/>
+      <c r="O24" s="101"/>
+      <c r="P24" s="102"/>
+    </row>
+    <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="103" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" s="104" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="120" t="n">
+        <v>706651018</v>
+      </c>
+      <c r="D25" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E25" s="107"/>
+      <c r="F25" s="108" t="n">
+        <v>12050</v>
+      </c>
+      <c r="G25" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H25" s="106"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="118"/>
+      <c r="K25" s="107"/>
+      <c r="L25" s="110"/>
+      <c r="M25" s="110"/>
+      <c r="N25" s="110"/>
+      <c r="O25" s="141"/>
+      <c r="P25" s="119"/>
+    </row>
+    <row r="26" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="88" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" s="95" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="133" t="n">
+        <v>718723801</v>
+      </c>
+      <c r="D26" s="97" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E26" s="98"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H26" s="97"/>
+      <c r="I26" s="97"/>
+      <c r="J26" s="118"/>
+      <c r="K26" s="98"/>
+      <c r="L26" s="88"/>
+      <c r="M26" s="88"/>
+      <c r="N26" s="88"/>
+      <c r="O26" s="101"/>
+      <c r="P26" s="142"/>
+    </row>
+    <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="103" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" s="104" t="s">
+        <v>154</v>
+      </c>
+      <c r="C27" s="105" t="n">
+        <v>729400661</v>
+      </c>
+      <c r="D27" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E27" s="107"/>
+      <c r="F27" s="108" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G27" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H27" s="143"/>
+      <c r="I27" s="106"/>
+      <c r="J27" s="118"/>
+      <c r="K27" s="107"/>
+      <c r="L27" s="110"/>
+      <c r="M27" s="110"/>
+      <c r="N27" s="110"/>
+      <c r="O27" s="101"/>
+      <c r="P27" s="102"/>
+    </row>
+    <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="103" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" s="104" t="s">
+        <v>419</v>
+      </c>
+      <c r="C28" s="105" t="n">
+        <v>101921686</v>
+      </c>
+      <c r="D28" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E28" s="107"/>
+      <c r="F28" s="108"/>
+      <c r="G28" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H28" s="106"/>
+      <c r="I28" s="106"/>
+      <c r="J28" s="118"/>
+      <c r="K28" s="107"/>
+      <c r="L28" s="110"/>
+      <c r="M28" s="110"/>
+      <c r="N28" s="110"/>
+      <c r="O28" s="144"/>
+      <c r="P28" s="102"/>
+    </row>
+    <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="103" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" s="104" t="s">
+        <v>384</v>
+      </c>
+      <c r="C29" s="96" t="n">
+        <v>713985999</v>
+      </c>
+      <c r="D29" s="106" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E29" s="107"/>
+      <c r="F29" s="108" t="n">
+        <v>750</v>
+      </c>
+      <c r="G29" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H29" s="106"/>
+      <c r="I29" s="106"/>
+      <c r="J29" s="118"/>
+      <c r="K29" s="107"/>
+      <c r="L29" s="92"/>
+      <c r="M29" s="92"/>
+      <c r="N29" s="92"/>
+      <c r="O29" s="101"/>
+      <c r="P29" s="145"/>
+    </row>
+    <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="146" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" s="95" t="s">
+        <v>422</v>
+      </c>
+      <c r="C30" s="120" t="n">
+        <v>717334827</v>
+      </c>
+      <c r="D30" s="147" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E30" s="148"/>
+      <c r="F30" s="149" t="n">
+        <v>6250</v>
+      </c>
+      <c r="G30" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H30" s="147"/>
+      <c r="I30" s="147"/>
+      <c r="J30" s="118"/>
+      <c r="K30" s="148"/>
+      <c r="L30" s="92"/>
+      <c r="M30" s="92"/>
+      <c r="N30" s="92"/>
+      <c r="O30" s="101"/>
+      <c r="P30" s="150"/>
+    </row>
+    <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="151" t="n">
+        <v>25</v>
+      </c>
+      <c r="B31" s="152" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="153" t="n">
+        <v>712298540</v>
+      </c>
+      <c r="D31" s="154" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E31" s="154"/>
+      <c r="F31" s="155" t="n">
+        <v>17750</v>
+      </c>
+      <c r="G31" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H31" s="154"/>
+      <c r="I31" s="154"/>
+      <c r="J31" s="118"/>
+      <c r="K31" s="154"/>
+      <c r="L31" s="92"/>
+      <c r="M31" s="92"/>
+      <c r="N31" s="92"/>
+      <c r="O31" s="101"/>
+      <c r="P31" s="102"/>
+    </row>
+    <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="151" t="n">
+        <v>26</v>
+      </c>
+      <c r="B32" s="95" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="153" t="n">
+        <v>114717120</v>
+      </c>
+      <c r="D32" s="154" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E32" s="154" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F32" s="155"/>
+      <c r="G32" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H32" s="154"/>
+      <c r="I32" s="154"/>
+      <c r="J32" s="118"/>
+      <c r="K32" s="154"/>
+      <c r="L32" s="92"/>
+      <c r="M32" s="92"/>
+      <c r="N32" s="92"/>
+      <c r="O32" s="101"/>
+      <c r="P32" s="102"/>
+    </row>
+    <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="151" t="n">
+        <v>27</v>
+      </c>
+      <c r="B33" s="156" t="s">
+        <v>425</v>
+      </c>
+      <c r="C33" s="157" t="s">
+        <v>426</v>
+      </c>
+      <c r="D33" s="154" t="n">
+        <v>12250</v>
+      </c>
+      <c r="E33" s="154"/>
+      <c r="F33" s="155"/>
+      <c r="G33" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H33" s="154"/>
+      <c r="I33" s="154"/>
+      <c r="J33" s="118"/>
+      <c r="K33" s="154"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+      <c r="N33" s="92"/>
+      <c r="O33" s="101"/>
+      <c r="P33" s="145"/>
+    </row>
+    <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="151" t="n">
+        <v>28</v>
+      </c>
+      <c r="B34" s="152" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="153" t="n">
+        <v>713597010</v>
+      </c>
+      <c r="D34" s="154" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E34" s="154"/>
+      <c r="F34" s="155" t="n">
+        <v>19500</v>
+      </c>
+      <c r="G34" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H34" s="154"/>
+      <c r="I34" s="154"/>
+      <c r="J34" s="118"/>
+      <c r="K34" s="154"/>
+      <c r="L34" s="158"/>
+      <c r="N34" s="159"/>
+      <c r="O34" s="101"/>
+      <c r="P34" s="102"/>
+    </row>
+    <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="151" t="n">
+        <v>29</v>
+      </c>
+      <c r="B35" s="152" t="s">
+        <v>388</v>
+      </c>
+      <c r="C35" s="153" t="n">
+        <v>726516413</v>
+      </c>
+      <c r="D35" s="154" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E35" s="154"/>
+      <c r="F35" s="155"/>
+      <c r="G35" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H35" s="154"/>
+      <c r="I35" s="154"/>
+      <c r="J35" s="118"/>
+      <c r="K35" s="154"/>
+      <c r="L35" s="92"/>
+      <c r="M35" s="92"/>
+      <c r="N35" s="92"/>
+      <c r="O35" s="144"/>
+      <c r="P35" s="160"/>
+    </row>
+    <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="151" t="n">
+        <v>30</v>
+      </c>
+      <c r="B36" s="152" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="157" t="n">
+        <v>713171316</v>
+      </c>
+      <c r="D36" s="154" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E36" s="154"/>
+      <c r="F36" s="155" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G36" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H36" s="154"/>
+      <c r="I36" s="154"/>
+      <c r="J36" s="161"/>
+      <c r="K36" s="154"/>
+      <c r="L36" s="92"/>
+      <c r="M36" s="92"/>
+      <c r="N36" s="92"/>
+      <c r="O36" s="137"/>
+      <c r="P36" s="102"/>
+    </row>
+    <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="109" t="n">
+        <v>31</v>
+      </c>
+      <c r="B37" s="95" t="s">
+        <v>435</v>
+      </c>
+      <c r="C37" s="133" t="s">
+        <v>425</v>
+      </c>
+      <c r="D37" s="109" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E37" s="109"/>
+      <c r="F37" s="162" t="n">
+        <v>12250</v>
+      </c>
+      <c r="G37" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H37" s="109"/>
+      <c r="I37" s="109"/>
+      <c r="J37" s="118"/>
+      <c r="K37" s="88"/>
+      <c r="L37" s="162"/>
+      <c r="M37" s="88"/>
+      <c r="N37" s="88"/>
+      <c r="O37" s="101"/>
+      <c r="P37" s="102"/>
+    </row>
+    <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="109" t="n">
+        <v>32</v>
+      </c>
+      <c r="B38" s="95" t="s">
+        <v>435</v>
+      </c>
+      <c r="C38" s="133" t="n">
+        <v>707653219</v>
+      </c>
+      <c r="D38" s="100" t="n">
+        <v>11750</v>
+      </c>
+      <c r="E38" s="88"/>
+      <c r="F38" s="163"/>
+      <c r="G38" s="98" t="n">
+        <v>250</v>
+      </c>
+      <c r="H38" s="109"/>
+      <c r="I38" s="109"/>
+      <c r="J38" s="161"/>
+      <c r="K38" s="88"/>
+      <c r="L38" s="88"/>
+      <c r="M38" s="88"/>
+      <c r="N38" s="88"/>
+      <c r="O38" s="101"/>
+      <c r="P38" s="102"/>
+    </row>
+    <row r="39" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="88"/>
+      <c r="B39" s="109"/>
+      <c r="C39" s="100"/>
+      <c r="D39" s="164" t="n">
+        <f aca="false">SUM(D7:D38)</f>
+        <v>341000</v>
+      </c>
+      <c r="E39" s="165" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F39" s="165"/>
+      <c r="G39" s="165" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H39" s="165"/>
+      <c r="I39" s="165"/>
+      <c r="J39" s="100" t="n">
+        <f aca="false">SUM(J7:J38)</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="165"/>
+      <c r="L39" s="165"/>
+      <c r="M39" s="165"/>
+      <c r="N39" s="165"/>
+      <c r="O39" s="166"/>
+      <c r="P39" s="88"/>
+    </row>
+    <row r="40" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="167" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="167" t="n">
+        <f aca="false">SUM(J8:J38)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="168"/>
+    </row>
+    <row r="41" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="109" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="109"/>
+      <c r="D41" s="169"/>
+      <c r="F41" s="170"/>
+      <c r="G41" s="170"/>
+      <c r="H41" s="170"/>
+    </row>
+    <row r="42" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="109"/>
+      <c r="C42" s="100"/>
+      <c r="F42" s="170"/>
+      <c r="G42" s="170"/>
+      <c r="H42" s="170"/>
+    </row>
+    <row r="43" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="169" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="171"/>
+      <c r="F43" s="170"/>
+      <c r="G43" s="170"/>
+      <c r="H43" s="170"/>
+    </row>
+    <row r="44" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="109"/>
+      <c r="C44" s="109"/>
+    </row>
+    <row r="45" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="109" t="s">
+        <v>438</v>
+      </c>
+      <c r="C45" s="109"/>
+    </row>
+    <row r="46" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="109" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="109"/>
+    </row>
+    <row r="47" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="109" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" s="109"/>
+    </row>
+    <row r="48" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="109" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" s="109"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">

--- a/PROPERTIES/QYOTA/QYOTA 2025.xlsx
+++ b/PROPERTIES/QYOTA/QYOTA 2025.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="446">
   <si>
     <t xml:space="preserve">COURTLAND REALTORS LTD P.O.BOX 11993, NAIROBI</t>
   </si>
@@ -1347,13 +1347,34 @@
   </si>
   <si>
     <t xml:space="preserve">MGT COMM 5% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THB1VPSK43 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH40XT5422 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH685P44AK </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH41TV5C0T </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH615KICID </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THB6W8TJJO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THBOTGFOT6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-??_-;_-@_-"/>
@@ -1361,8 +1382,9 @@
     <numFmt numFmtId="168" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="169" formatCode="#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00"/>
+    <numFmt numFmtId="171" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1630,6 +1652,37 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF00A933"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1716,7 +1769,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="186">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2405,6 +2458,62 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="37" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="39" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="37" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5703,7 +5812,7 @@
       <c r="M7" s="88"/>
       <c r="N7" s="88"/>
       <c r="O7" s="101"/>
-      <c r="P7" s="102"/>
+      <c r="P7" s="172"/>
     </row>
     <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="103" t="n">
@@ -5733,7 +5842,7 @@
       <c r="M8" s="110"/>
       <c r="N8" s="110"/>
       <c r="O8" s="101"/>
-      <c r="P8" s="111"/>
+      <c r="P8" s="173"/>
     </row>
     <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="112" t="n">
@@ -5763,7 +5872,7 @@
       <c r="M9" s="110"/>
       <c r="N9" s="110"/>
       <c r="O9" s="101"/>
-      <c r="P9" s="119"/>
+      <c r="P9" s="174"/>
     </row>
     <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="103" t="n">
@@ -5791,7 +5900,7 @@
       <c r="M10" s="110"/>
       <c r="N10" s="110"/>
       <c r="O10" s="101"/>
-      <c r="P10" s="102"/>
+      <c r="P10" s="172"/>
     </row>
     <row r="11" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="121" t="n">
@@ -5815,7 +5924,7 @@
       <c r="M11" s="128"/>
       <c r="N11" s="128"/>
       <c r="O11" s="129"/>
-      <c r="P11" s="130"/>
+      <c r="P11" s="175"/>
     </row>
     <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="103" t="n">
@@ -5843,7 +5952,7 @@
       <c r="M12" s="110"/>
       <c r="N12" s="110"/>
       <c r="O12" s="101"/>
-      <c r="P12" s="102"/>
+      <c r="P12" s="172"/>
     </row>
     <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="103" t="n">
@@ -5871,7 +5980,7 @@
       <c r="M13" s="110"/>
       <c r="N13" s="110"/>
       <c r="O13" s="101"/>
-      <c r="P13" s="119"/>
+      <c r="P13" s="174"/>
     </row>
     <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="103" t="n">
@@ -5901,7 +6010,7 @@
       <c r="M14" s="110"/>
       <c r="N14" s="110"/>
       <c r="O14" s="101"/>
-      <c r="P14" s="119"/>
+      <c r="P14" s="174"/>
     </row>
     <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="88" t="n">
@@ -5929,7 +6038,7 @@
       <c r="M15" s="92"/>
       <c r="N15" s="92"/>
       <c r="O15" s="101"/>
-      <c r="P15" s="134"/>
+      <c r="P15" s="176"/>
     </row>
     <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="88" t="n">
@@ -5953,13 +6062,19 @@
       </c>
       <c r="H16" s="97"/>
       <c r="I16" s="97"/>
-      <c r="J16" s="118"/>
+      <c r="J16" s="118" t="n">
+        <v>10500</v>
+      </c>
       <c r="K16" s="98"/>
       <c r="L16" s="135"/>
       <c r="M16" s="92"/>
       <c r="N16" s="92"/>
-      <c r="O16" s="101"/>
-      <c r="P16" s="102"/>
+      <c r="O16" s="101" t="n">
+        <v>45969</v>
+      </c>
+      <c r="P16" s="172" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="103" t="n">
@@ -5987,7 +6102,7 @@
       <c r="M17" s="110"/>
       <c r="N17" s="110"/>
       <c r="O17" s="101"/>
-      <c r="P17" s="119"/>
+      <c r="P17" s="174"/>
     </row>
     <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="103" t="n">
@@ -6009,13 +6124,19 @@
       </c>
       <c r="H18" s="106"/>
       <c r="I18" s="106"/>
-      <c r="J18" s="118"/>
+      <c r="J18" s="118" t="n">
+        <v>11250</v>
+      </c>
       <c r="K18" s="107"/>
       <c r="L18" s="110"/>
       <c r="M18" s="110"/>
       <c r="N18" s="110"/>
-      <c r="O18" s="101"/>
-      <c r="P18" s="119"/>
+      <c r="O18" s="101" t="n">
+        <v>45755</v>
+      </c>
+      <c r="P18" s="177" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="103" t="n">
@@ -6045,7 +6166,7 @@
       <c r="M19" s="110"/>
       <c r="N19" s="110"/>
       <c r="O19" s="137"/>
-      <c r="P19" s="138"/>
+      <c r="P19" s="178"/>
     </row>
     <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="103" t="n">
@@ -6073,7 +6194,7 @@
       <c r="M20" s="110"/>
       <c r="N20" s="110"/>
       <c r="O20" s="101"/>
-      <c r="P20" s="140"/>
+      <c r="P20" s="179"/>
     </row>
     <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="112" t="n">
@@ -6103,7 +6224,7 @@
       <c r="M21" s="110"/>
       <c r="N21" s="110"/>
       <c r="O21" s="101"/>
-      <c r="P21" s="138"/>
+      <c r="P21" s="178"/>
     </row>
     <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="103" t="n">
@@ -6133,7 +6254,7 @@
       <c r="M22" s="110"/>
       <c r="N22" s="110"/>
       <c r="O22" s="101"/>
-      <c r="P22" s="102"/>
+      <c r="P22" s="172"/>
     </row>
     <row r="23" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="88" t="n">
@@ -6155,13 +6276,19 @@
       </c>
       <c r="H23" s="97"/>
       <c r="I23" s="97"/>
-      <c r="J23" s="118"/>
+      <c r="J23" s="118" t="n">
+        <v>11250</v>
+      </c>
       <c r="K23" s="98"/>
       <c r="L23" s="92"/>
       <c r="M23" s="92"/>
       <c r="N23" s="92"/>
-      <c r="O23" s="101"/>
-      <c r="P23" s="111"/>
+      <c r="O23" s="101" t="n">
+        <v>45816</v>
+      </c>
+      <c r="P23" s="173" t="s">
+        <v>441</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="88" t="n">
@@ -6183,13 +6310,19 @@
       </c>
       <c r="H24" s="97"/>
       <c r="I24" s="97"/>
-      <c r="J24" s="118"/>
+      <c r="J24" s="118" t="n">
+        <v>11250</v>
+      </c>
       <c r="K24" s="98"/>
       <c r="L24" s="135"/>
       <c r="M24" s="92"/>
       <c r="N24" s="92"/>
-      <c r="O24" s="101"/>
-      <c r="P24" s="102"/>
+      <c r="O24" s="101" t="n">
+        <v>45755</v>
+      </c>
+      <c r="P24" s="172" t="s">
+        <v>442</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="103" t="n">
@@ -6219,7 +6352,7 @@
       <c r="M25" s="110"/>
       <c r="N25" s="110"/>
       <c r="O25" s="141"/>
-      <c r="P25" s="119"/>
+      <c r="P25" s="174"/>
     </row>
     <row r="26" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="88" t="n">
@@ -6241,13 +6374,19 @@
       </c>
       <c r="H26" s="97"/>
       <c r="I26" s="97"/>
-      <c r="J26" s="118"/>
+      <c r="J26" s="118" t="n">
+        <v>11250</v>
+      </c>
       <c r="K26" s="98"/>
       <c r="L26" s="88"/>
       <c r="M26" s="88"/>
       <c r="N26" s="88"/>
-      <c r="O26" s="101"/>
-      <c r="P26" s="142"/>
+      <c r="O26" s="101" t="n">
+        <v>45816</v>
+      </c>
+      <c r="P26" s="180" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="103" t="n">
@@ -6277,7 +6416,7 @@
       <c r="M27" s="110"/>
       <c r="N27" s="110"/>
       <c r="O27" s="101"/>
-      <c r="P27" s="102"/>
+      <c r="P27" s="172"/>
     </row>
     <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="103" t="n">
@@ -6305,7 +6444,7 @@
       <c r="M28" s="110"/>
       <c r="N28" s="110"/>
       <c r="O28" s="144"/>
-      <c r="P28" s="102"/>
+      <c r="P28" s="172"/>
     </row>
     <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="103" t="n">
@@ -6329,13 +6468,19 @@
       </c>
       <c r="H29" s="106"/>
       <c r="I29" s="106"/>
-      <c r="J29" s="118"/>
+      <c r="J29" s="118" t="n">
+        <v>11250</v>
+      </c>
       <c r="K29" s="107"/>
       <c r="L29" s="92"/>
       <c r="M29" s="92"/>
       <c r="N29" s="92"/>
-      <c r="O29" s="101"/>
-      <c r="P29" s="145"/>
+      <c r="O29" s="101" t="n">
+        <v>45969</v>
+      </c>
+      <c r="P29" s="181" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="146" t="n">
@@ -6365,7 +6510,7 @@
       <c r="M30" s="92"/>
       <c r="N30" s="92"/>
       <c r="O30" s="101"/>
-      <c r="P30" s="150"/>
+      <c r="P30" s="182"/>
     </row>
     <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="151" t="n">
@@ -6395,7 +6540,7 @@
       <c r="M31" s="92"/>
       <c r="N31" s="92"/>
       <c r="O31" s="101"/>
-      <c r="P31" s="102"/>
+      <c r="P31" s="172"/>
     </row>
     <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="151" t="n">
@@ -6425,7 +6570,7 @@
       <c r="M32" s="92"/>
       <c r="N32" s="92"/>
       <c r="O32" s="101"/>
-      <c r="P32" s="102"/>
+      <c r="P32" s="172"/>
     </row>
     <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="151" t="n">
@@ -6453,7 +6598,7 @@
       <c r="M33" s="92"/>
       <c r="N33" s="92"/>
       <c r="O33" s="101"/>
-      <c r="P33" s="145"/>
+      <c r="P33" s="181"/>
     </row>
     <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="151" t="n">
@@ -6482,7 +6627,7 @@
       <c r="L34" s="158"/>
       <c r="N34" s="159"/>
       <c r="O34" s="101"/>
-      <c r="P34" s="102"/>
+      <c r="P34" s="172"/>
     </row>
     <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="151" t="n">
@@ -6510,7 +6655,7 @@
       <c r="M35" s="92"/>
       <c r="N35" s="92"/>
       <c r="O35" s="144"/>
-      <c r="P35" s="160"/>
+      <c r="P35" s="183"/>
     </row>
     <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="151" t="n">
@@ -6534,13 +6679,19 @@
       </c>
       <c r="H36" s="154"/>
       <c r="I36" s="154"/>
-      <c r="J36" s="161"/>
+      <c r="J36" s="184" t="n">
+        <v>12250</v>
+      </c>
       <c r="K36" s="154"/>
       <c r="L36" s="92"/>
       <c r="M36" s="92"/>
       <c r="N36" s="92"/>
-      <c r="O36" s="137"/>
-      <c r="P36" s="102"/>
+      <c r="O36" s="185" t="n">
+        <v>45969</v>
+      </c>
+      <c r="P36" s="172" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="109" t="n">
@@ -6570,7 +6721,7 @@
       <c r="M37" s="88"/>
       <c r="N37" s="88"/>
       <c r="O37" s="101"/>
-      <c r="P37" s="102"/>
+      <c r="P37" s="172"/>
     </row>
     <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="109" t="n">
@@ -6598,7 +6749,7 @@
       <c r="M38" s="88"/>
       <c r="N38" s="88"/>
       <c r="O38" s="101"/>
-      <c r="P38" s="102"/>
+      <c r="P38" s="172"/>
     </row>
     <row r="39" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="88"/>
@@ -6619,14 +6770,14 @@
       <c r="I39" s="165"/>
       <c r="J39" s="100" t="n">
         <f aca="false">SUM(J7:J38)</f>
-        <v>0</v>
+        <v>79000</v>
       </c>
       <c r="K39" s="165"/>
       <c r="L39" s="165"/>
       <c r="M39" s="165"/>
       <c r="N39" s="165"/>
       <c r="O39" s="166"/>
-      <c r="P39" s="88"/>
+      <c r="P39" s="172"/>
     </row>
     <row r="40" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="167" t="s">
@@ -6634,7 +6785,7 @@
       </c>
       <c r="C40" s="167" t="n">
         <f aca="false">SUM(J8:J38)</f>
-        <v>0</v>
+        <v>79000</v>
       </c>
       <c r="E40" s="168"/>
     </row>

--- a/PROPERTIES/QYOTA/QYOTA 2025.xlsx
+++ b/PROPERTIES/QYOTA/QYOTA 2025.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="OCT" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="447">
   <si>
     <t xml:space="preserve">COURTLAND REALTORS LTD P.O.BOX 11993, NAIROBI</t>
   </si>
@@ -1347,6 +1347,9 @@
   </si>
   <si>
     <t xml:space="preserve">MGT COMM 5% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH71ANML01</t>
   </si>
   <si>
     <t xml:space="preserve">THB1VPSK43 </t>
@@ -6032,13 +6035,19 @@
       </c>
       <c r="H15" s="97"/>
       <c r="I15" s="97"/>
-      <c r="J15" s="118"/>
+      <c r="J15" s="118" t="n">
+        <v>11250</v>
+      </c>
       <c r="K15" s="98"/>
       <c r="L15" s="92"/>
       <c r="M15" s="92"/>
       <c r="N15" s="92"/>
-      <c r="O15" s="101"/>
-      <c r="P15" s="176"/>
+      <c r="O15" s="101" t="n">
+        <v>45846</v>
+      </c>
+      <c r="P15" s="176" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="88" t="n">
@@ -6073,7 +6082,7 @@
         <v>45969</v>
       </c>
       <c r="P16" s="172" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6135,7 +6144,7 @@
         <v>45755</v>
       </c>
       <c r="P18" s="177" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6287,7 +6296,7 @@
         <v>45816</v>
       </c>
       <c r="P23" s="173" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6321,7 +6330,7 @@
         <v>45755</v>
       </c>
       <c r="P24" s="172" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6385,7 +6394,7 @@
         <v>45816</v>
       </c>
       <c r="P26" s="180" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6479,7 +6488,7 @@
         <v>45969</v>
       </c>
       <c r="P29" s="181" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6690,7 +6699,7 @@
         <v>45969</v>
       </c>
       <c r="P36" s="172" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6770,7 +6779,7 @@
       <c r="I39" s="165"/>
       <c r="J39" s="100" t="n">
         <f aca="false">SUM(J7:J38)</f>
-        <v>79000</v>
+        <v>90250</v>
       </c>
       <c r="K39" s="165"/>
       <c r="L39" s="165"/>
@@ -6785,7 +6794,7 @@
       </c>
       <c r="C40" s="167" t="n">
         <f aca="false">SUM(J8:J38)</f>
-        <v>79000</v>
+        <v>90250</v>
       </c>
       <c r="E40" s="168"/>
     </row>

--- a/PROPERTIES/QYOTA/QYOTA 2025.xlsx
+++ b/PROPERTIES/QYOTA/QYOTA 2025.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="OCT" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="460">
   <si>
     <t xml:space="preserve">COURTLAND REALTORS LTD P.O.BOX 11993, NAIROBI</t>
   </si>
@@ -1349,15 +1349,33 @@
     <t xml:space="preserve">MGT COMM 5% </t>
   </si>
   <si>
+    <t xml:space="preserve">TH46XNOE1Q </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THC9372CRN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THK24GTKGC</t>
+  </si>
+  <si>
     <t xml:space="preserve">TH71ANML01</t>
   </si>
   <si>
     <t xml:space="preserve">THB1VPSK43 </t>
   </si>
   <si>
+    <t xml:space="preserve">TH511AXN9F </t>
+  </si>
+  <si>
     <t xml:space="preserve">TH40XT5422 </t>
   </si>
   <si>
+    <t xml:space="preserve">TH522WP68O </t>
+  </si>
+  <si>
     <t xml:space="preserve">TH685P44AK </t>
   </si>
   <si>
@@ -1367,10 +1385,31 @@
     <t xml:space="preserve">TH615KICID </t>
   </si>
   <si>
+    <t xml:space="preserve">TH13ET7M97 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MENDRINE</t>
+  </si>
+  <si>
     <t xml:space="preserve">THB6W8TJJO </t>
   </si>
   <si>
+    <t xml:space="preserve">TH84FWTZQC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THH7SI7FO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH25KCV0YX </t>
+  </si>
+  <si>
     <t xml:space="preserve">THBOTGFOT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTX25214PBBOL </t>
   </si>
 </sst>
 </file>
@@ -5869,13 +5908,19 @@
       </c>
       <c r="H9" s="115"/>
       <c r="I9" s="115"/>
-      <c r="J9" s="118"/>
+      <c r="J9" s="118" t="n">
+        <v>10250</v>
+      </c>
       <c r="K9" s="116"/>
       <c r="L9" s="110"/>
       <c r="M9" s="110"/>
       <c r="N9" s="110"/>
-      <c r="O9" s="101"/>
-      <c r="P9" s="174"/>
+      <c r="O9" s="101" t="n">
+        <v>45755</v>
+      </c>
+      <c r="P9" s="174" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="103" t="n">
@@ -5916,9 +5961,7 @@
       <c r="D11" s="124"/>
       <c r="E11" s="125"/>
       <c r="F11" s="126"/>
-      <c r="G11" s="125" t="n">
-        <v>250</v>
-      </c>
+      <c r="G11" s="125"/>
       <c r="H11" s="124"/>
       <c r="I11" s="124"/>
       <c r="J11" s="127"/>
@@ -5949,13 +5992,19 @@
       </c>
       <c r="H12" s="103"/>
       <c r="I12" s="103"/>
-      <c r="J12" s="118"/>
+      <c r="J12" s="118" t="n">
+        <v>9500</v>
+      </c>
       <c r="K12" s="103"/>
       <c r="L12" s="110"/>
       <c r="M12" s="110"/>
       <c r="N12" s="110"/>
-      <c r="O12" s="101"/>
-      <c r="P12" s="172"/>
+      <c r="O12" s="101" t="n">
+        <v>45999</v>
+      </c>
+      <c r="P12" s="172" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="103" t="n">
@@ -5977,13 +6026,19 @@
       </c>
       <c r="H13" s="106"/>
       <c r="I13" s="106"/>
-      <c r="J13" s="118"/>
+      <c r="J13" s="118" t="n">
+        <v>9500</v>
+      </c>
       <c r="K13" s="107"/>
       <c r="L13" s="110"/>
       <c r="M13" s="110"/>
       <c r="N13" s="110"/>
-      <c r="O13" s="101"/>
-      <c r="P13" s="174"/>
+      <c r="O13" s="101" t="s">
+        <v>441</v>
+      </c>
+      <c r="P13" s="174" t="s">
+        <v>442</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="103" t="n">
@@ -6046,7 +6101,7 @@
         <v>45846</v>
       </c>
       <c r="P15" s="176" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6082,7 +6137,7 @@
         <v>45969</v>
       </c>
       <c r="P16" s="172" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6105,13 +6160,19 @@
       </c>
       <c r="H17" s="106"/>
       <c r="I17" s="106"/>
-      <c r="J17" s="118"/>
+      <c r="J17" s="118" t="n">
+        <v>11250</v>
+      </c>
       <c r="K17" s="107"/>
       <c r="L17" s="110"/>
       <c r="M17" s="110"/>
       <c r="N17" s="110"/>
-      <c r="O17" s="101"/>
-      <c r="P17" s="174"/>
+      <c r="O17" s="101" t="n">
+        <v>45785</v>
+      </c>
+      <c r="P17" s="174" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="103" t="n">
@@ -6144,7 +6205,7 @@
         <v>45755</v>
       </c>
       <c r="P18" s="177" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6197,13 +6258,19 @@
       </c>
       <c r="H20" s="139"/>
       <c r="I20" s="139"/>
-      <c r="J20" s="118"/>
+      <c r="J20" s="118" t="n">
+        <v>11250</v>
+      </c>
       <c r="K20" s="103"/>
       <c r="L20" s="110"/>
       <c r="M20" s="110"/>
       <c r="N20" s="110"/>
-      <c r="O20" s="101"/>
-      <c r="P20" s="179"/>
+      <c r="O20" s="101" t="n">
+        <v>45785</v>
+      </c>
+      <c r="P20" s="179" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="112" t="n">
@@ -6296,7 +6363,7 @@
         <v>45816</v>
       </c>
       <c r="P23" s="173" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6330,7 +6397,7 @@
         <v>45755</v>
       </c>
       <c r="P24" s="172" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6394,7 +6461,7 @@
         <v>45816</v>
       </c>
       <c r="P26" s="180" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6419,20 +6486,26 @@
       </c>
       <c r="H27" s="143"/>
       <c r="I27" s="106"/>
-      <c r="J27" s="118"/>
+      <c r="J27" s="118" t="n">
+        <v>10750</v>
+      </c>
       <c r="K27" s="107"/>
       <c r="L27" s="110"/>
       <c r="M27" s="110"/>
       <c r="N27" s="110"/>
-      <c r="O27" s="101"/>
-      <c r="P27" s="172"/>
+      <c r="O27" s="101" t="n">
+        <v>45665</v>
+      </c>
+      <c r="P27" s="172" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="103" t="n">
         <v>22</v>
       </c>
       <c r="B28" s="104" t="s">
-        <v>419</v>
+        <v>452</v>
       </c>
       <c r="C28" s="105" t="n">
         <v>101921686</v>
@@ -6447,13 +6520,19 @@
       </c>
       <c r="H28" s="106"/>
       <c r="I28" s="106"/>
-      <c r="J28" s="118"/>
+      <c r="J28" s="118" t="n">
+        <v>11250</v>
+      </c>
       <c r="K28" s="107"/>
       <c r="L28" s="110"/>
       <c r="M28" s="110"/>
       <c r="N28" s="110"/>
-      <c r="O28" s="144"/>
-      <c r="P28" s="172"/>
+      <c r="O28" s="144" t="n">
+        <v>45969</v>
+      </c>
+      <c r="P28" s="172" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="103" t="n">
@@ -6488,7 +6567,7 @@
         <v>45969</v>
       </c>
       <c r="P29" s="181" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6513,13 +6592,19 @@
       </c>
       <c r="H30" s="147"/>
       <c r="I30" s="147"/>
-      <c r="J30" s="118"/>
+      <c r="J30" s="118" t="n">
+        <v>11250</v>
+      </c>
       <c r="K30" s="148"/>
       <c r="L30" s="92"/>
       <c r="M30" s="92"/>
       <c r="N30" s="92"/>
-      <c r="O30" s="101"/>
-      <c r="P30" s="182"/>
+      <c r="O30" s="101" t="n">
+        <v>45877</v>
+      </c>
+      <c r="P30" s="182" t="s">
+        <v>454</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="151" t="n">
@@ -6631,12 +6716,18 @@
       </c>
       <c r="H34" s="154"/>
       <c r="I34" s="154"/>
-      <c r="J34" s="118"/>
+      <c r="J34" s="118" t="n">
+        <v>12250</v>
+      </c>
       <c r="K34" s="154"/>
       <c r="L34" s="158"/>
       <c r="N34" s="159"/>
-      <c r="O34" s="101"/>
-      <c r="P34" s="172"/>
+      <c r="O34" s="101" t="s">
+        <v>455</v>
+      </c>
+      <c r="P34" s="172" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="151" t="n">
@@ -6658,13 +6749,19 @@
       </c>
       <c r="H35" s="154"/>
       <c r="I35" s="154"/>
-      <c r="J35" s="118"/>
+      <c r="J35" s="118" t="n">
+        <v>12500</v>
+      </c>
       <c r="K35" s="154"/>
       <c r="L35" s="92"/>
       <c r="M35" s="92"/>
       <c r="N35" s="92"/>
-      <c r="O35" s="144"/>
-      <c r="P35" s="183"/>
+      <c r="O35" s="144" t="n">
+        <v>45696</v>
+      </c>
+      <c r="P35" s="183" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="151" t="n">
@@ -6699,7 +6796,7 @@
         <v>45969</v>
       </c>
       <c r="P36" s="172" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6752,13 +6849,19 @@
       </c>
       <c r="H38" s="109"/>
       <c r="I38" s="109"/>
-      <c r="J38" s="161"/>
+      <c r="J38" s="161" t="n">
+        <v>12250</v>
+      </c>
       <c r="K38" s="88"/>
       <c r="L38" s="88"/>
       <c r="M38" s="88"/>
       <c r="N38" s="88"/>
-      <c r="O38" s="101"/>
-      <c r="P38" s="172"/>
+      <c r="O38" s="101" t="s">
+        <v>455</v>
+      </c>
+      <c r="P38" s="172" t="s">
+        <v>459</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="88"/>
@@ -6779,7 +6882,7 @@
       <c r="I39" s="165"/>
       <c r="J39" s="100" t="n">
         <f aca="false">SUM(J7:J38)</f>
-        <v>90250</v>
+        <v>212250</v>
       </c>
       <c r="K39" s="165"/>
       <c r="L39" s="165"/>
@@ -6794,7 +6897,7 @@
       </c>
       <c r="C40" s="167" t="n">
         <f aca="false">SUM(J8:J38)</f>
-        <v>90250</v>
+        <v>212250</v>
       </c>
       <c r="E40" s="168"/>
     </row>
